--- a/public/5to Secundaria Guindo.xlsx
+++ b/public/5to Secundaria Guindo.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
   <si>
     <t>CUADRO GENERAL DE NOTAS</t>
   </si>
@@ -138,6 +138,9 @@
     <t>LEDEZMA ARAOZ IGNACIO</t>
   </si>
   <si>
+    <t>LONGPRE - KINGSTON BYRON</t>
+  </si>
+  <si>
     <t>MARQUEZ VAN DER VEEN PEDRO</t>
   </si>
   <si>
@@ -213,7 +216,7 @@
     <t>1 de 2</t>
   </si>
   <si>
-    <t>Generado el : 08/04/2026</t>
+    <t>Generado el : 05/05/2026</t>
   </si>
 </sst>
 </file>
@@ -2220,17 +2223,17 @@
         <v>30</v>
       </c>
       <c r="C8" s="33">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
       <c r="F8" s="21">
         <f>IF(SUM(C8:E8)=0,"",ROUND(AVERAGE(C8:E8),0))</f>
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G8" s="19">
         <f>IF(BQ8="","",BQ8)</f>
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H8" s="19" t="str">
         <f>IF(BR8="","",BR8)</f>
@@ -2242,52 +2245,52 @@
       </c>
       <c r="J8" s="22">
         <f>IF(BT8="","",BT8)</f>
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K8" s="18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L8" s="19"/>
       <c r="M8" s="20"/>
-      <c r="N8" s="21" t="str">
+      <c r="N8" s="21">
         <f>IF(SUM(K8:M8)=0,"",ROUND(AVERAGE(K8:M8),0))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="O8" s="19">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="P8" s="19"/>
       <c r="Q8" s="20"/>
       <c r="R8" s="22">
         <f>IF(SUM(O8:Q8)=0,"",ROUND(AVERAGE(O8:Q8),0))</f>
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S8" s="18">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="T8" s="19"/>
       <c r="U8" s="20"/>
       <c r="V8" s="21">
         <f>IF(SUM(S8:U8)=0,"",ROUND(AVERAGE(S8:U8),0))</f>
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="W8" s="18">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="X8" s="19"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="21">
         <f>IF(SUM(W8:Y8)=0,"",ROUND(AVERAGE(W8:Y8),0))</f>
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="AA8" s="19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AB8" s="19"/>
       <c r="AC8" s="20"/>
       <c r="AD8" s="22">
         <f>IF(SUM(AA8:AC8)=0,"",ROUND(AVERAGE(AA8:AC8),0))</f>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AE8" s="18"/>
       <c r="AF8" s="19"/>
@@ -2297,56 +2300,58 @@
         <v/>
       </c>
       <c r="AI8" s="18">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AJ8" s="19"/>
       <c r="AK8" s="20"/>
       <c r="AL8" s="21">
         <f>IF(SUM(AI8:AK8)=0,"",ROUND(AVERAGE(AI8:AK8),0))</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AM8" s="18">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AN8" s="19"/>
       <c r="AO8" s="20"/>
       <c r="AP8" s="21">
         <f>IF(SUM(AM8:AO8)=0,"",ROUND(AVERAGE(AM8:AO8),0))</f>
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AQ8" s="18">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="AR8" s="19"/>
       <c r="AS8" s="20"/>
       <c r="AT8" s="21">
         <f>IF(SUM(AQ8:AS8)=0,"",ROUND(AVERAGE(AQ8:AS8),0))</f>
-        <v>19</v>
-      </c>
-      <c r="AU8" s="18"/>
+        <v>52</v>
+      </c>
+      <c r="AU8" s="18">
+        <v>48</v>
+      </c>
       <c r="AV8" s="19"/>
       <c r="AW8" s="20"/>
-      <c r="AX8" s="21" t="str">
+      <c r="AX8" s="21">
         <f>IF(SUM(AU8:AW8)=0,"",ROUND(AVERAGE(AU8:AW8),0))</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="AY8" s="19">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AZ8" s="19"/>
       <c r="BA8" s="20"/>
       <c r="BB8" s="22">
         <f>IF(SUM(AY8:BA8)=0,"",ROUND(AVERAGE(AY8:BA8),0))</f>
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC8" s="23">
-        <v>26.0</v>
+        <v>48.0</v>
       </c>
       <c r="BD8" s="24"/>
       <c r="BE8" s="25"/>
       <c r="BF8" s="26">
         <f>IF(SUM(F8,J8,N8,R8,V8,Z8,AD8,AH8,AL8,AP8,AT8,AX8,BB8)=0,"",ROUND(AVERAGE(F8,J8,N8,R8,V8,Z8,AD8,AH8,AL8,AP8,AT8,AX8,BB8),2))</f>
-        <v>33.9</v>
+        <v>52</v>
       </c>
       <c r="BG8" s="16">
         <v>1</v>
@@ -2356,31 +2361,31 @@
         <v>- GARCIA PEREZ ALAN RODRIGO</v>
       </c>
       <c r="BI8" s="29">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BJ8" s="27"/>
       <c r="BK8" s="28"/>
       <c r="BL8" s="30">
         <f>IF(SUM(BI8:BK8)=0,"",ROUND(AVERAGE(BI8:BK8),0))</f>
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BM8" s="29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BN8" s="27"/>
       <c r="BO8" s="28"/>
-      <c r="BP8" s="30" t="str">
+      <c r="BP8" s="30">
         <f>IF(SUM(BM8:BO8)=0,"",ROUND(AVERAGE(BM8:BO8),0))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="BQ8" s="18">
-        <v>14.0</v>
+        <v>42.0</v>
       </c>
       <c r="BR8" s="19"/>
       <c r="BS8" s="20"/>
       <c r="BT8" s="21">
         <f>IF(SUM(BQ8:BS8)=0,"",ROUND(AVERAGE(BQ8:BS8),0))</f>
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2391,17 +2396,17 @@
         <v>31</v>
       </c>
       <c r="C9" s="33">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="35"/>
       <c r="F9" s="36">
         <f>IF(SUM(C9:E9)=0,"",ROUND(AVERAGE(C9:E9),0))</f>
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G9" s="34">
         <f>IF(BQ9="","",BQ9)</f>
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H9" s="34" t="str">
         <f>IF(BR9="","",BR9)</f>
@@ -2413,52 +2418,52 @@
       </c>
       <c r="J9" s="37">
         <f>IF(BT9="","",BT9)</f>
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="K9" s="33">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L9" s="34"/>
       <c r="M9" s="35"/>
-      <c r="N9" s="36" t="str">
+      <c r="N9" s="36">
         <f>IF(SUM(K9:M9)=0,"",ROUND(AVERAGE(K9:M9),0))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="O9" s="34">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="P9" s="34"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="37">
         <f>IF(SUM(O9:Q9)=0,"",ROUND(AVERAGE(O9:Q9),0))</f>
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="S9" s="33">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="T9" s="34"/>
       <c r="U9" s="35"/>
       <c r="V9" s="36">
         <f>IF(SUM(S9:U9)=0,"",ROUND(AVERAGE(S9:U9),0))</f>
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="W9" s="33">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="X9" s="34"/>
       <c r="Y9" s="35"/>
       <c r="Z9" s="36">
         <f>IF(SUM(W9:Y9)=0,"",ROUND(AVERAGE(W9:Y9),0))</f>
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="AA9" s="34">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="AB9" s="34"/>
       <c r="AC9" s="35"/>
       <c r="AD9" s="37">
         <f>IF(SUM(AA9:AC9)=0,"",ROUND(AVERAGE(AA9:AC9),0))</f>
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="AE9" s="33"/>
       <c r="AF9" s="34"/>
@@ -2468,56 +2473,58 @@
         <v/>
       </c>
       <c r="AI9" s="33">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ9" s="34"/>
       <c r="AK9" s="35"/>
       <c r="AL9" s="36">
         <f>IF(SUM(AI9:AK9)=0,"",ROUND(AVERAGE(AI9:AK9),0))</f>
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AM9" s="33">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AN9" s="34"/>
       <c r="AO9" s="35"/>
       <c r="AP9" s="36">
         <f>IF(SUM(AM9:AO9)=0,"",ROUND(AVERAGE(AM9:AO9),0))</f>
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AQ9" s="33">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="AR9" s="34"/>
       <c r="AS9" s="35"/>
       <c r="AT9" s="36">
         <f>IF(SUM(AQ9:AS9)=0,"",ROUND(AVERAGE(AQ9:AS9),0))</f>
-        <v>64</v>
-      </c>
-      <c r="AU9" s="33"/>
+        <v>77</v>
+      </c>
+      <c r="AU9" s="33">
+        <v>80</v>
+      </c>
       <c r="AV9" s="34"/>
       <c r="AW9" s="35"/>
-      <c r="AX9" s="36" t="str">
+      <c r="AX9" s="36">
         <f>IF(SUM(AU9:AW9)=0,"",ROUND(AVERAGE(AU9:AW9),0))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="AY9" s="34">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="AZ9" s="34"/>
       <c r="BA9" s="35"/>
       <c r="BB9" s="37">
         <f>IF(SUM(AY9:BA9)=0,"",ROUND(AVERAGE(AY9:BA9),0))</f>
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="BC9" s="38">
-        <v>44.0</v>
+        <v>76.0</v>
       </c>
       <c r="BD9" s="39"/>
       <c r="BE9" s="40"/>
       <c r="BF9" s="41">
         <f>IF(SUM(F9,J9,N9,R9,V9,Z9,AD9,AH9,AL9,AP9,AT9,AX9,BB9)=0,"",ROUND(AVERAGE(F9,J9,N9,R9,V9,Z9,AD9,AH9,AL9,AP9,AT9,AX9,BB9),2))</f>
-        <v>57.2</v>
+        <v>82.83</v>
       </c>
       <c r="BG9" s="31">
         <v>2</v>
@@ -2527,31 +2534,31 @@
         <v>AGUIRRE PEREZ LUCIANA RAFAELA</v>
       </c>
       <c r="BI9" s="44">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="BJ9" s="42"/>
       <c r="BK9" s="43"/>
       <c r="BL9" s="45">
         <f>IF(SUM(BI9:BK9)=0,"",ROUND(AVERAGE(BI9:BK9),0))</f>
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="BM9" s="44">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BN9" s="42"/>
       <c r="BO9" s="43"/>
-      <c r="BP9" s="45" t="str">
+      <c r="BP9" s="45">
         <f>IF(SUM(BM9:BO9)=0,"",ROUND(AVERAGE(BM9:BO9),0))</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="BQ9" s="33">
-        <v>35.0</v>
+        <v>85.0</v>
       </c>
       <c r="BR9" s="34"/>
       <c r="BS9" s="35"/>
       <c r="BT9" s="36">
         <f>IF(SUM(BQ9:BS9)=0,"",ROUND(AVERAGE(BQ9:BS9),0))</f>
-        <v>35</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2562,17 +2569,17 @@
         <v>32</v>
       </c>
       <c r="C10" s="33">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="35"/>
       <c r="F10" s="36">
         <f>IF(SUM(C10:E10)=0,"",ROUND(AVERAGE(C10:E10),0))</f>
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G10" s="34">
         <f>IF(BQ10="","",BQ10)</f>
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="H10" s="34" t="str">
         <f>IF(BR10="","",BR10)</f>
@@ -2584,52 +2591,52 @@
       </c>
       <c r="J10" s="37">
         <f>IF(BT10="","",BT10)</f>
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="K10" s="33">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35"/>
-      <c r="N10" s="36" t="str">
+      <c r="N10" s="36">
         <f>IF(SUM(K10:M10)=0,"",ROUND(AVERAGE(K10:M10),0))</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="O10" s="34">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="35"/>
       <c r="R10" s="37">
         <f>IF(SUM(O10:Q10)=0,"",ROUND(AVERAGE(O10:Q10),0))</f>
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="S10" s="33">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="T10" s="34"/>
       <c r="U10" s="35"/>
       <c r="V10" s="36">
         <f>IF(SUM(S10:U10)=0,"",ROUND(AVERAGE(S10:U10),0))</f>
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="W10" s="33">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="X10" s="34"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="36">
         <f>IF(SUM(W10:Y10)=0,"",ROUND(AVERAGE(W10:Y10),0))</f>
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA10" s="34">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AB10" s="34"/>
       <c r="AC10" s="35"/>
       <c r="AD10" s="37">
         <f>IF(SUM(AA10:AC10)=0,"",ROUND(AVERAGE(AA10:AC10),0))</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AE10" s="33"/>
       <c r="AF10" s="34"/>
@@ -2639,56 +2646,58 @@
         <v/>
       </c>
       <c r="AI10" s="33">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="AJ10" s="34"/>
       <c r="AK10" s="35"/>
       <c r="AL10" s="36">
         <f>IF(SUM(AI10:AK10)=0,"",ROUND(AVERAGE(AI10:AK10),0))</f>
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="AM10" s="33">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="AN10" s="34"/>
       <c r="AO10" s="35"/>
       <c r="AP10" s="36">
         <f>IF(SUM(AM10:AO10)=0,"",ROUND(AVERAGE(AM10:AO10),0))</f>
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="AQ10" s="33">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="AR10" s="34"/>
       <c r="AS10" s="35"/>
       <c r="AT10" s="36">
         <f>IF(SUM(AQ10:AS10)=0,"",ROUND(AVERAGE(AQ10:AS10),0))</f>
-        <v>18</v>
-      </c>
-      <c r="AU10" s="33"/>
+        <v>61</v>
+      </c>
+      <c r="AU10" s="33">
+        <v>67</v>
+      </c>
       <c r="AV10" s="34"/>
       <c r="AW10" s="35"/>
-      <c r="AX10" s="36" t="str">
+      <c r="AX10" s="36">
         <f>IF(SUM(AU10:AW10)=0,"",ROUND(AVERAGE(AU10:AW10),0))</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="AY10" s="34">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AZ10" s="34"/>
       <c r="BA10" s="35"/>
       <c r="BB10" s="37">
         <f>IF(SUM(AY10:BA10)=0,"",ROUND(AVERAGE(AY10:BA10),0))</f>
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="BC10" s="38">
-        <v>35.0</v>
+        <v>66.0</v>
       </c>
       <c r="BD10" s="39"/>
       <c r="BE10" s="40"/>
       <c r="BF10" s="41">
         <f>IF(SUM(F10,J10,N10,R10,V10,Z10,AD10,AH10,AL10,AP10,AT10,AX10,BB10)=0,"",ROUND(AVERAGE(F10,J10,N10,R10,V10,Z10,AD10,AH10,AL10,AP10,AT10,AX10,BB10),2))</f>
-        <v>46.1</v>
+        <v>71.75</v>
       </c>
       <c r="BG10" s="31">
         <v>3</v>
@@ -2698,31 +2707,31 @@
         <v>AREVALO ANDRADE MAXIMILIANO</v>
       </c>
       <c r="BI10" s="44">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="BJ10" s="42"/>
       <c r="BK10" s="43"/>
       <c r="BL10" s="45">
         <f>IF(SUM(BI10:BK10)=0,"",ROUND(AVERAGE(BI10:BK10),0))</f>
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="BM10" s="44">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="BN10" s="42"/>
       <c r="BO10" s="43"/>
-      <c r="BP10" s="45" t="str">
+      <c r="BP10" s="45">
         <f>IF(SUM(BM10:BO10)=0,"",ROUND(AVERAGE(BM10:BO10),0))</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="BQ10" s="33">
-        <v>30.0</v>
+        <v>70.0</v>
       </c>
       <c r="BR10" s="34"/>
       <c r="BS10" s="35"/>
       <c r="BT10" s="36">
         <f>IF(SUM(BQ10:BS10)=0,"",ROUND(AVERAGE(BQ10:BS10),0))</f>
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -2733,17 +2742,17 @@
         <v>33</v>
       </c>
       <c r="C11" s="33">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="35"/>
       <c r="F11" s="36">
         <f>IF(SUM(C11:E11)=0,"",ROUND(AVERAGE(C11:E11),0))</f>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G11" s="34">
         <f>IF(BQ11="","",BQ11)</f>
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="H11" s="34" t="str">
         <f>IF(BR11="","",BR11)</f>
@@ -2755,52 +2764,52 @@
       </c>
       <c r="J11" s="37">
         <f>IF(BT11="","",BT11)</f>
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="K11" s="33">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="35"/>
-      <c r="N11" s="36" t="str">
+      <c r="N11" s="36">
         <f>IF(SUM(K11:M11)=0,"",ROUND(AVERAGE(K11:M11),0))</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="O11" s="34">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="P11" s="34"/>
       <c r="Q11" s="35"/>
       <c r="R11" s="37">
         <f>IF(SUM(O11:Q11)=0,"",ROUND(AVERAGE(O11:Q11),0))</f>
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="S11" s="33">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T11" s="34"/>
       <c r="U11" s="35"/>
       <c r="V11" s="36">
         <f>IF(SUM(S11:U11)=0,"",ROUND(AVERAGE(S11:U11),0))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="W11" s="33">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="X11" s="34"/>
       <c r="Y11" s="35"/>
       <c r="Z11" s="36">
         <f>IF(SUM(W11:Y11)=0,"",ROUND(AVERAGE(W11:Y11),0))</f>
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="AA11" s="34">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="AB11" s="34"/>
       <c r="AC11" s="35"/>
       <c r="AD11" s="37">
         <f>IF(SUM(AA11:AC11)=0,"",ROUND(AVERAGE(AA11:AC11),0))</f>
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="AE11" s="33"/>
       <c r="AF11" s="34"/>
@@ -2810,56 +2819,58 @@
         <v/>
       </c>
       <c r="AI11" s="33">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AJ11" s="34"/>
       <c r="AK11" s="35"/>
       <c r="AL11" s="36">
         <f>IF(SUM(AI11:AK11)=0,"",ROUND(AVERAGE(AI11:AK11),0))</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AM11" s="33">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="AN11" s="34"/>
       <c r="AO11" s="35"/>
       <c r="AP11" s="36">
         <f>IF(SUM(AM11:AO11)=0,"",ROUND(AVERAGE(AM11:AO11),0))</f>
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="AQ11" s="33">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AR11" s="34"/>
       <c r="AS11" s="35"/>
       <c r="AT11" s="36">
         <f>IF(SUM(AQ11:AS11)=0,"",ROUND(AVERAGE(AQ11:AS11),0))</f>
-        <v>85</v>
-      </c>
-      <c r="AU11" s="33"/>
+        <v>87</v>
+      </c>
+      <c r="AU11" s="33">
+        <v>76</v>
+      </c>
       <c r="AV11" s="34"/>
       <c r="AW11" s="35"/>
-      <c r="AX11" s="36" t="str">
+      <c r="AX11" s="36">
         <f>IF(SUM(AU11:AW11)=0,"",ROUND(AVERAGE(AU11:AW11),0))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="AY11" s="34">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="AZ11" s="34"/>
       <c r="BA11" s="35"/>
       <c r="BB11" s="37">
         <f>IF(SUM(AY11:BA11)=0,"",ROUND(AVERAGE(AY11:BA11),0))</f>
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="BC11" s="38">
-        <v>51.0</v>
+        <v>82.0</v>
       </c>
       <c r="BD11" s="39"/>
       <c r="BE11" s="40"/>
       <c r="BF11" s="41">
         <f>IF(SUM(F11,J11,N11,R11,V11,Z11,AD11,AH11,AL11,AP11,AT11,AX11,BB11)=0,"",ROUND(AVERAGE(F11,J11,N11,R11,V11,Z11,AD11,AH11,AL11,AP11,AT11,AX11,BB11),2))</f>
-        <v>66.7</v>
+        <v>88.75</v>
       </c>
       <c r="BG11" s="31">
         <v>4</v>
@@ -2869,31 +2880,31 @@
         <v>ASSEFF VELASCO MIA ROSARIO</v>
       </c>
       <c r="BI11" s="44">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="BJ11" s="42"/>
       <c r="BK11" s="43"/>
       <c r="BL11" s="45">
         <f>IF(SUM(BI11:BK11)=0,"",ROUND(AVERAGE(BI11:BK11),0))</f>
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="BM11" s="44">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BN11" s="42"/>
       <c r="BO11" s="43"/>
-      <c r="BP11" s="45" t="str">
+      <c r="BP11" s="45">
         <f>IF(SUM(BM11:BO11)=0,"",ROUND(AVERAGE(BM11:BO11),0))</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="BQ11" s="33">
-        <v>34.0</v>
+        <v>86.0</v>
       </c>
       <c r="BR11" s="34"/>
       <c r="BS11" s="35"/>
       <c r="BT11" s="36">
         <f>IF(SUM(BQ11:BS11)=0,"",ROUND(AVERAGE(BQ11:BS11),0))</f>
-        <v>34</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -2904,17 +2915,17 @@
         <v>34</v>
       </c>
       <c r="C12" s="33">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D12" s="34"/>
       <c r="E12" s="35"/>
-      <c r="F12" s="36">
+      <c r="F12" s="36" t="str">
         <f>IF(SUM(C12:E12)=0,"",ROUND(AVERAGE(C12:E12),0))</f>
-        <v>57</v>
+        <v/>
       </c>
       <c r="G12" s="34">
         <f>IF(BQ12="","",BQ12)</f>
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="H12" s="34" t="str">
         <f>IF(BR12="","",BR12)</f>
@@ -2926,52 +2937,52 @@
       </c>
       <c r="J12" s="37">
         <f>IF(BT12="","",BT12)</f>
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="K12" s="33">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35"/>
-      <c r="N12" s="36" t="str">
+      <c r="N12" s="36">
         <f>IF(SUM(K12:M12)=0,"",ROUND(AVERAGE(K12:M12),0))</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="O12" s="34">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="P12" s="34"/>
       <c r="Q12" s="35"/>
       <c r="R12" s="37">
         <f>IF(SUM(O12:Q12)=0,"",ROUND(AVERAGE(O12:Q12),0))</f>
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="S12" s="33">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="T12" s="34"/>
       <c r="U12" s="35"/>
       <c r="V12" s="36">
         <f>IF(SUM(S12:U12)=0,"",ROUND(AVERAGE(S12:U12),0))</f>
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="W12" s="33">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="X12" s="34"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="36">
         <f>IF(SUM(W12:Y12)=0,"",ROUND(AVERAGE(W12:Y12),0))</f>
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="AA12" s="34">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AB12" s="34"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="37">
         <f>IF(SUM(AA12:AC12)=0,"",ROUND(AVERAGE(AA12:AC12),0))</f>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AE12" s="33"/>
       <c r="AF12" s="34"/>
@@ -2981,56 +2992,58 @@
         <v/>
       </c>
       <c r="AI12" s="33">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="35"/>
       <c r="AL12" s="36">
         <f>IF(SUM(AI12:AK12)=0,"",ROUND(AVERAGE(AI12:AK12),0))</f>
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AM12" s="33">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="AN12" s="34"/>
       <c r="AO12" s="35"/>
       <c r="AP12" s="36">
         <f>IF(SUM(AM12:AO12)=0,"",ROUND(AVERAGE(AM12:AO12),0))</f>
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="AQ12" s="33">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="AR12" s="34"/>
       <c r="AS12" s="35"/>
       <c r="AT12" s="36">
         <f>IF(SUM(AQ12:AS12)=0,"",ROUND(AVERAGE(AQ12:AS12),0))</f>
-        <v>29</v>
-      </c>
-      <c r="AU12" s="33"/>
+        <v>51</v>
+      </c>
+      <c r="AU12" s="33">
+        <v>56</v>
+      </c>
       <c r="AV12" s="34"/>
       <c r="AW12" s="35"/>
-      <c r="AX12" s="36" t="str">
+      <c r="AX12" s="36">
         <f>IF(SUM(AU12:AW12)=0,"",ROUND(AVERAGE(AU12:AW12),0))</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="AY12" s="34">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="AZ12" s="34"/>
       <c r="BA12" s="35"/>
       <c r="BB12" s="37">
         <f>IF(SUM(AY12:BA12)=0,"",ROUND(AVERAGE(AY12:BA12),0))</f>
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="BC12" s="38">
-        <v>35.0</v>
+        <v>56.0</v>
       </c>
       <c r="BD12" s="39"/>
       <c r="BE12" s="40"/>
       <c r="BF12" s="41">
         <f>IF(SUM(F12,J12,N12,R12,V12,Z12,AD12,AH12,AL12,AP12,AT12,AX12,BB12)=0,"",ROUND(AVERAGE(F12,J12,N12,R12,V12,Z12,AD12,AH12,AL12,AP12,AT12,AX12,BB12),2))</f>
-        <v>45</v>
+        <v>66.36</v>
       </c>
       <c r="BG12" s="31">
         <v>5</v>
@@ -3040,31 +3053,31 @@
         <v>CACERES MANCILLA VALENTINA</v>
       </c>
       <c r="BI12" s="44">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="BJ12" s="42"/>
       <c r="BK12" s="43"/>
       <c r="BL12" s="45">
         <f>IF(SUM(BI12:BK12)=0,"",ROUND(AVERAGE(BI12:BK12),0))</f>
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="BM12" s="44">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="BN12" s="42"/>
       <c r="BO12" s="43"/>
-      <c r="BP12" s="45" t="str">
+      <c r="BP12" s="45">
         <f>IF(SUM(BM12:BO12)=0,"",ROUND(AVERAGE(BM12:BO12),0))</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="BQ12" s="33">
-        <v>25.0</v>
+        <v>73.0</v>
       </c>
       <c r="BR12" s="34"/>
       <c r="BS12" s="35"/>
       <c r="BT12" s="36">
         <f>IF(SUM(BQ12:BS12)=0,"",ROUND(AVERAGE(BQ12:BS12),0))</f>
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3075,17 +3088,17 @@
         <v>35</v>
       </c>
       <c r="C13" s="33">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="35"/>
-      <c r="F13" s="36">
+      <c r="F13" s="36" t="str">
         <f>IF(SUM(C13:E13)=0,"",ROUND(AVERAGE(C13:E13),0))</f>
-        <v>51</v>
+        <v/>
       </c>
       <c r="G13" s="34">
         <f>IF(BQ13="","",BQ13)</f>
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="H13" s="34" t="str">
         <f>IF(BR13="","",BR13)</f>
@@ -3097,52 +3110,52 @@
       </c>
       <c r="J13" s="37">
         <f>IF(BT13="","",BT13)</f>
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K13" s="33">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35"/>
-      <c r="N13" s="36" t="str">
+      <c r="N13" s="36">
         <f>IF(SUM(K13:M13)=0,"",ROUND(AVERAGE(K13:M13),0))</f>
-        <v/>
+        <v>74</v>
       </c>
       <c r="O13" s="34">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="35"/>
       <c r="R13" s="37">
         <f>IF(SUM(O13:Q13)=0,"",ROUND(AVERAGE(O13:Q13),0))</f>
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="S13" s="33">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T13" s="34"/>
       <c r="U13" s="35"/>
       <c r="V13" s="36">
         <f>IF(SUM(S13:U13)=0,"",ROUND(AVERAGE(S13:U13),0))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="W13" s="33">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="X13" s="34"/>
       <c r="Y13" s="35"/>
       <c r="Z13" s="36">
         <f>IF(SUM(W13:Y13)=0,"",ROUND(AVERAGE(W13:Y13),0))</f>
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="AA13" s="34">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AB13" s="34"/>
       <c r="AC13" s="35"/>
       <c r="AD13" s="37">
         <f>IF(SUM(AA13:AC13)=0,"",ROUND(AVERAGE(AA13:AC13),0))</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AE13" s="33"/>
       <c r="AF13" s="34"/>
@@ -3152,56 +3165,58 @@
         <v/>
       </c>
       <c r="AI13" s="33">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AJ13" s="34"/>
       <c r="AK13" s="35"/>
       <c r="AL13" s="36">
         <f>IF(SUM(AI13:AK13)=0,"",ROUND(AVERAGE(AI13:AK13),0))</f>
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AM13" s="33">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="AN13" s="34"/>
       <c r="AO13" s="35"/>
       <c r="AP13" s="36">
         <f>IF(SUM(AM13:AO13)=0,"",ROUND(AVERAGE(AM13:AO13),0))</f>
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="AQ13" s="33">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AR13" s="34"/>
       <c r="AS13" s="35"/>
       <c r="AT13" s="36">
         <f>IF(SUM(AQ13:AS13)=0,"",ROUND(AVERAGE(AQ13:AS13),0))</f>
-        <v>84</v>
-      </c>
-      <c r="AU13" s="33"/>
+        <v>88</v>
+      </c>
+      <c r="AU13" s="33">
+        <v>94</v>
+      </c>
       <c r="AV13" s="34"/>
       <c r="AW13" s="35"/>
-      <c r="AX13" s="36" t="str">
+      <c r="AX13" s="36">
         <f>IF(SUM(AU13:AW13)=0,"",ROUND(AVERAGE(AU13:AW13),0))</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="AY13" s="34">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="AZ13" s="34"/>
       <c r="BA13" s="35"/>
       <c r="BB13" s="37">
         <f>IF(SUM(AY13:BA13)=0,"",ROUND(AVERAGE(AY13:BA13),0))</f>
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="BC13" s="38">
-        <v>49.0</v>
+        <v>72.0</v>
       </c>
       <c r="BD13" s="39"/>
       <c r="BE13" s="40"/>
       <c r="BF13" s="41">
         <f>IF(SUM(F13,J13,N13,R13,V13,Z13,AD13,AH13,AL13,AP13,AT13,AX13,BB13)=0,"",ROUND(AVERAGE(F13,J13,N13,R13,V13,Z13,AD13,AH13,AL13,AP13,AT13,AX13,BB13),2))</f>
-        <v>64.2</v>
+        <v>85.64</v>
       </c>
       <c r="BG13" s="31">
         <v>6</v>
@@ -3211,31 +3226,31 @@
         <v>CARTAGENA PACHECO RAFAELA</v>
       </c>
       <c r="BI13" s="44">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="BJ13" s="42"/>
       <c r="BK13" s="43"/>
       <c r="BL13" s="45">
         <f>IF(SUM(BI13:BK13)=0,"",ROUND(AVERAGE(BI13:BK13),0))</f>
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="BM13" s="44">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BN13" s="42"/>
       <c r="BO13" s="43"/>
-      <c r="BP13" s="45" t="str">
+      <c r="BP13" s="45">
         <f>IF(SUM(BM13:BO13)=0,"",ROUND(AVERAGE(BM13:BO13),0))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="BQ13" s="33">
-        <v>30.0</v>
+        <v>81.0</v>
       </c>
       <c r="BR13" s="34"/>
       <c r="BS13" s="35"/>
       <c r="BT13" s="36">
         <f>IF(SUM(BQ13:BS13)=0,"",ROUND(AVERAGE(BQ13:BS13),0))</f>
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3246,17 +3261,17 @@
         <v>36</v>
       </c>
       <c r="C14" s="33">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="35"/>
-      <c r="F14" s="36">
+      <c r="F14" s="36" t="str">
         <f>IF(SUM(C14:E14)=0,"",ROUND(AVERAGE(C14:E14),0))</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="G14" s="34">
         <f>IF(BQ14="","",BQ14)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H14" s="34" t="str">
         <f>IF(BR14="","",BR14)</f>
@@ -3268,52 +3283,52 @@
       </c>
       <c r="J14" s="37">
         <f>IF(BT14="","",BT14)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K14" s="33">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35"/>
-      <c r="N14" s="36" t="str">
+      <c r="N14" s="36">
         <f>IF(SUM(K14:M14)=0,"",ROUND(AVERAGE(K14:M14),0))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="O14" s="34">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="35"/>
       <c r="R14" s="37">
         <f>IF(SUM(O14:Q14)=0,"",ROUND(AVERAGE(O14:Q14),0))</f>
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="S14" s="33">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="T14" s="34"/>
       <c r="U14" s="35"/>
       <c r="V14" s="36">
         <f>IF(SUM(S14:U14)=0,"",ROUND(AVERAGE(S14:U14),0))</f>
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="W14" s="33">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="X14" s="34"/>
       <c r="Y14" s="35"/>
       <c r="Z14" s="36">
         <f>IF(SUM(W14:Y14)=0,"",ROUND(AVERAGE(W14:Y14),0))</f>
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="AA14" s="34">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="AB14" s="34"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="37">
         <f>IF(SUM(AA14:AC14)=0,"",ROUND(AVERAGE(AA14:AC14),0))</f>
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="AE14" s="33"/>
       <c r="AF14" s="34"/>
@@ -3323,56 +3338,58 @@
         <v/>
       </c>
       <c r="AI14" s="33">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="AJ14" s="34"/>
       <c r="AK14" s="35"/>
       <c r="AL14" s="36">
         <f>IF(SUM(AI14:AK14)=0,"",ROUND(AVERAGE(AI14:AK14),0))</f>
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="AM14" s="33">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AN14" s="34"/>
       <c r="AO14" s="35"/>
       <c r="AP14" s="36">
         <f>IF(SUM(AM14:AO14)=0,"",ROUND(AVERAGE(AM14:AO14),0))</f>
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AQ14" s="33">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AR14" s="34"/>
       <c r="AS14" s="35"/>
       <c r="AT14" s="36">
         <f>IF(SUM(AQ14:AS14)=0,"",ROUND(AVERAGE(AQ14:AS14),0))</f>
-        <v>21</v>
-      </c>
-      <c r="AU14" s="33"/>
+        <v>52</v>
+      </c>
+      <c r="AU14" s="33">
+        <v>52</v>
+      </c>
       <c r="AV14" s="34"/>
       <c r="AW14" s="35"/>
-      <c r="AX14" s="36" t="str">
+      <c r="AX14" s="36">
         <f>IF(SUM(AU14:AW14)=0,"",ROUND(AVERAGE(AU14:AW14),0))</f>
-        <v/>
+        <v>52</v>
       </c>
       <c r="AY14" s="34">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="AZ14" s="34"/>
       <c r="BA14" s="35"/>
       <c r="BB14" s="37">
         <f>IF(SUM(AY14:BA14)=0,"",ROUND(AVERAGE(AY14:BA14),0))</f>
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="BC14" s="38">
-        <v>28.0</v>
+        <v>53.0</v>
       </c>
       <c r="BD14" s="39"/>
       <c r="BE14" s="40"/>
       <c r="BF14" s="41">
         <f>IF(SUM(F14,J14,N14,R14,V14,Z14,AD14,AH14,AL14,AP14,AT14,AX14,BB14)=0,"",ROUND(AVERAGE(F14,J14,N14,R14,V14,Z14,AD14,AH14,AL14,AP14,AT14,AX14,BB14),2))</f>
-        <v>36.7</v>
+        <v>62.18</v>
       </c>
       <c r="BG14" s="31">
         <v>7</v>
@@ -3382,31 +3399,31 @@
         <v>CASSAB HERNANDEZ JOSE</v>
       </c>
       <c r="BI14" s="44">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="BJ14" s="42"/>
       <c r="BK14" s="43"/>
       <c r="BL14" s="45">
         <f>IF(SUM(BI14:BK14)=0,"",ROUND(AVERAGE(BI14:BK14),0))</f>
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="BM14" s="44">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BN14" s="42"/>
       <c r="BO14" s="43"/>
-      <c r="BP14" s="45" t="str">
+      <c r="BP14" s="45">
         <f>IF(SUM(BM14:BO14)=0,"",ROUND(AVERAGE(BM14:BO14),0))</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="BQ14" s="33">
-        <v>31.0</v>
+        <v>48.0</v>
       </c>
       <c r="BR14" s="34"/>
       <c r="BS14" s="35"/>
       <c r="BT14" s="36">
         <f>IF(SUM(BQ14:BS14)=0,"",ROUND(AVERAGE(BQ14:BS14),0))</f>
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -3417,17 +3434,17 @@
         <v>37</v>
       </c>
       <c r="C15" s="33">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D15" s="34"/>
       <c r="E15" s="35"/>
-      <c r="F15" s="36">
+      <c r="F15" s="36" t="str">
         <f>IF(SUM(C15:E15)=0,"",ROUND(AVERAGE(C15:E15),0))</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="G15" s="34">
         <f>IF(BQ15="","",BQ15)</f>
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="H15" s="34" t="str">
         <f>IF(BR15="","",BR15)</f>
@@ -3439,52 +3456,52 @@
       </c>
       <c r="J15" s="37">
         <f>IF(BT15="","",BT15)</f>
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="K15" s="33">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35"/>
-      <c r="N15" s="36" t="str">
+      <c r="N15" s="36">
         <f>IF(SUM(K15:M15)=0,"",ROUND(AVERAGE(K15:M15),0))</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="O15" s="34">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="35"/>
       <c r="R15" s="37">
         <f>IF(SUM(O15:Q15)=0,"",ROUND(AVERAGE(O15:Q15),0))</f>
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="S15" s="33">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T15" s="34"/>
       <c r="U15" s="35"/>
       <c r="V15" s="36">
         <f>IF(SUM(S15:U15)=0,"",ROUND(AVERAGE(S15:U15),0))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="W15" s="33">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="X15" s="34"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="36">
         <f>IF(SUM(W15:Y15)=0,"",ROUND(AVERAGE(W15:Y15),0))</f>
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="AA15" s="34">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AB15" s="34"/>
       <c r="AC15" s="35"/>
       <c r="AD15" s="37">
         <f>IF(SUM(AA15:AC15)=0,"",ROUND(AVERAGE(AA15:AC15),0))</f>
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AE15" s="33"/>
       <c r="AF15" s="34"/>
@@ -3494,56 +3511,58 @@
         <v/>
       </c>
       <c r="AI15" s="33">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AJ15" s="34"/>
       <c r="AK15" s="35"/>
       <c r="AL15" s="36">
         <f>IF(SUM(AI15:AK15)=0,"",ROUND(AVERAGE(AI15:AK15),0))</f>
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AM15" s="33">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="AN15" s="34"/>
       <c r="AO15" s="35"/>
       <c r="AP15" s="36">
         <f>IF(SUM(AM15:AO15)=0,"",ROUND(AVERAGE(AM15:AO15),0))</f>
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="AQ15" s="33">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="AR15" s="34"/>
       <c r="AS15" s="35"/>
       <c r="AT15" s="36">
         <f>IF(SUM(AQ15:AS15)=0,"",ROUND(AVERAGE(AQ15:AS15),0))</f>
-        <v>33</v>
-      </c>
-      <c r="AU15" s="33"/>
+        <v>62</v>
+      </c>
+      <c r="AU15" s="33">
+        <v>79</v>
+      </c>
       <c r="AV15" s="34"/>
       <c r="AW15" s="35"/>
-      <c r="AX15" s="36" t="str">
+      <c r="AX15" s="36">
         <f>IF(SUM(AU15:AW15)=0,"",ROUND(AVERAGE(AU15:AW15),0))</f>
-        <v/>
+        <v>79</v>
       </c>
       <c r="AY15" s="34">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AZ15" s="34"/>
       <c r="BA15" s="35"/>
       <c r="BB15" s="37">
         <f>IF(SUM(AY15:BA15)=0,"",ROUND(AVERAGE(AY15:BA15),0))</f>
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="BC15" s="38">
-        <v>32.0</v>
+        <v>65.0</v>
       </c>
       <c r="BD15" s="39"/>
       <c r="BE15" s="40"/>
       <c r="BF15" s="41">
         <f>IF(SUM(F15,J15,N15,R15,V15,Z15,AD15,AH15,AL15,AP15,AT15,AX15,BB15)=0,"",ROUND(AVERAGE(F15,J15,N15,R15,V15,Z15,AD15,AH15,AL15,AP15,AT15,AX15,BB15),2))</f>
-        <v>41.4</v>
+        <v>76.82</v>
       </c>
       <c r="BG15" s="31">
         <v>8</v>
@@ -3553,31 +3572,31 @@
         <v>FORNS SAMSO MORALES LUCAS</v>
       </c>
       <c r="BI15" s="44">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="BJ15" s="42"/>
       <c r="BK15" s="43"/>
       <c r="BL15" s="45">
         <f>IF(SUM(BI15:BK15)=0,"",ROUND(AVERAGE(BI15:BK15),0))</f>
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="BM15" s="44">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="BN15" s="42"/>
       <c r="BO15" s="43"/>
-      <c r="BP15" s="45" t="str">
+      <c r="BP15" s="45">
         <f>IF(SUM(BM15:BO15)=0,"",ROUND(AVERAGE(BM15:BO15),0))</f>
-        <v/>
+        <v>87</v>
       </c>
       <c r="BQ15" s="33">
-        <v>36.0</v>
+        <v>88.0</v>
       </c>
       <c r="BR15" s="34"/>
       <c r="BS15" s="35"/>
       <c r="BT15" s="36">
         <f>IF(SUM(BQ15:BS15)=0,"",ROUND(AVERAGE(BQ15:BS15),0))</f>
-        <v>36</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -3588,17 +3607,17 @@
         <v>38</v>
       </c>
       <c r="C16" s="33">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" s="34"/>
       <c r="E16" s="35"/>
-      <c r="F16" s="36">
+      <c r="F16" s="36" t="str">
         <f>IF(SUM(C16:E16)=0,"",ROUND(AVERAGE(C16:E16),0))</f>
-        <v>71</v>
+        <v/>
       </c>
       <c r="G16" s="34">
         <f>IF(BQ16="","",BQ16)</f>
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H16" s="34" t="str">
         <f>IF(BR16="","",BR16)</f>
@@ -3610,52 +3629,52 @@
       </c>
       <c r="J16" s="37">
         <f>IF(BT16="","",BT16)</f>
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="K16" s="33">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="36" t="str">
+      <c r="N16" s="36">
         <f>IF(SUM(K16:M16)=0,"",ROUND(AVERAGE(K16:M16),0))</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="O16" s="34">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="P16" s="34"/>
       <c r="Q16" s="35"/>
       <c r="R16" s="37">
         <f>IF(SUM(O16:Q16)=0,"",ROUND(AVERAGE(O16:Q16),0))</f>
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="S16" s="33">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T16" s="34"/>
       <c r="U16" s="35"/>
       <c r="V16" s="36">
         <f>IF(SUM(S16:U16)=0,"",ROUND(AVERAGE(S16:U16),0))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="W16" s="33">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="X16" s="34"/>
       <c r="Y16" s="35"/>
       <c r="Z16" s="36">
         <f>IF(SUM(W16:Y16)=0,"",ROUND(AVERAGE(W16:Y16),0))</f>
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="AA16" s="34">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="AB16" s="34"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="37">
         <f>IF(SUM(AA16:AC16)=0,"",ROUND(AVERAGE(AA16:AC16),0))</f>
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="AE16" s="33"/>
       <c r="AF16" s="34"/>
@@ -3665,56 +3684,58 @@
         <v/>
       </c>
       <c r="AI16" s="33">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AJ16" s="34"/>
       <c r="AK16" s="35"/>
       <c r="AL16" s="36">
         <f>IF(SUM(AI16:AK16)=0,"",ROUND(AVERAGE(AI16:AK16),0))</f>
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AM16" s="33">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AN16" s="34"/>
       <c r="AO16" s="35"/>
       <c r="AP16" s="36">
         <f>IF(SUM(AM16:AO16)=0,"",ROUND(AVERAGE(AM16:AO16),0))</f>
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AQ16" s="33">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AR16" s="34"/>
       <c r="AS16" s="35"/>
       <c r="AT16" s="36">
         <f>IF(SUM(AQ16:AS16)=0,"",ROUND(AVERAGE(AQ16:AS16),0))</f>
-        <v>78</v>
-      </c>
-      <c r="AU16" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="AU16" s="33">
+        <v>76</v>
+      </c>
       <c r="AV16" s="34"/>
       <c r="AW16" s="35"/>
-      <c r="AX16" s="36" t="str">
+      <c r="AX16" s="36">
         <f>IF(SUM(AU16:AW16)=0,"",ROUND(AVERAGE(AU16:AW16),0))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="AY16" s="34">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="AZ16" s="34"/>
       <c r="BA16" s="35"/>
       <c r="BB16" s="37">
         <f>IF(SUM(AY16:BA16)=0,"",ROUND(AVERAGE(AY16:BA16),0))</f>
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="BC16" s="38">
-        <v>51.0</v>
+        <v>76.0</v>
       </c>
       <c r="BD16" s="39"/>
       <c r="BE16" s="40"/>
       <c r="BF16" s="41">
         <f>IF(SUM(F16,J16,N16,R16,V16,Z16,AD16,AH16,AL16,AP16,AT16,AX16,BB16)=0,"",ROUND(AVERAGE(F16,J16,N16,R16,V16,Z16,AD16,AH16,AL16,AP16,AT16,AX16,BB16),2))</f>
-        <v>66.5</v>
+        <v>90.36</v>
       </c>
       <c r="BG16" s="31">
         <v>9</v>
@@ -3724,31 +3745,31 @@
         <v>LASTRA COLLAZOS SOFIA</v>
       </c>
       <c r="BI16" s="44">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="BJ16" s="42"/>
       <c r="BK16" s="43"/>
       <c r="BL16" s="45">
         <f>IF(SUM(BI16:BK16)=0,"",ROUND(AVERAGE(BI16:BK16),0))</f>
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="BM16" s="44">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BN16" s="42"/>
       <c r="BO16" s="43"/>
-      <c r="BP16" s="45" t="str">
+      <c r="BP16" s="45">
         <f>IF(SUM(BM16:BO16)=0,"",ROUND(AVERAGE(BM16:BO16),0))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="BQ16" s="33">
-        <v>39.0</v>
+        <v>92.0</v>
       </c>
       <c r="BR16" s="34"/>
       <c r="BS16" s="35"/>
       <c r="BT16" s="36">
         <f>IF(SUM(BQ16:BS16)=0,"",ROUND(AVERAGE(BQ16:BS16),0))</f>
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -3759,17 +3780,17 @@
         <v>39</v>
       </c>
       <c r="C17" s="33">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="35"/>
-      <c r="F17" s="36">
+      <c r="F17" s="36" t="str">
         <f>IF(SUM(C17:E17)=0,"",ROUND(AVERAGE(C17:E17),0))</f>
-        <v>55</v>
+        <v/>
       </c>
       <c r="G17" s="34">
         <f>IF(BQ17="","",BQ17)</f>
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H17" s="34" t="str">
         <f>IF(BR17="","",BR17)</f>
@@ -3781,52 +3802,52 @@
       </c>
       <c r="J17" s="37">
         <f>IF(BT17="","",BT17)</f>
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="K17" s="33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="36" t="str">
+      <c r="N17" s="36">
         <f>IF(SUM(K17:M17)=0,"",ROUND(AVERAGE(K17:M17),0))</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="O17" s="34">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="P17" s="34"/>
       <c r="Q17" s="35"/>
       <c r="R17" s="37">
         <f>IF(SUM(O17:Q17)=0,"",ROUND(AVERAGE(O17:Q17),0))</f>
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="S17" s="33">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="T17" s="34"/>
       <c r="U17" s="35"/>
       <c r="V17" s="36">
         <f>IF(SUM(S17:U17)=0,"",ROUND(AVERAGE(S17:U17),0))</f>
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="W17" s="33">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="X17" s="34"/>
       <c r="Y17" s="35"/>
       <c r="Z17" s="36">
         <f>IF(SUM(W17:Y17)=0,"",ROUND(AVERAGE(W17:Y17),0))</f>
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AA17" s="34">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AB17" s="34"/>
       <c r="AC17" s="35"/>
       <c r="AD17" s="37">
         <f>IF(SUM(AA17:AC17)=0,"",ROUND(AVERAGE(AA17:AC17),0))</f>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AE17" s="33"/>
       <c r="AF17" s="34"/>
@@ -3836,56 +3857,58 @@
         <v/>
       </c>
       <c r="AI17" s="33">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="AJ17" s="34"/>
       <c r="AK17" s="35"/>
       <c r="AL17" s="36">
         <f>IF(SUM(AI17:AK17)=0,"",ROUND(AVERAGE(AI17:AK17),0))</f>
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="AM17" s="33">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AN17" s="34"/>
       <c r="AO17" s="35"/>
       <c r="AP17" s="36">
         <f>IF(SUM(AM17:AO17)=0,"",ROUND(AVERAGE(AM17:AO17),0))</f>
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AQ17" s="33">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AR17" s="34"/>
       <c r="AS17" s="35"/>
       <c r="AT17" s="36">
         <f>IF(SUM(AQ17:AS17)=0,"",ROUND(AVERAGE(AQ17:AS17),0))</f>
-        <v>75</v>
-      </c>
-      <c r="AU17" s="33"/>
+        <v>87</v>
+      </c>
+      <c r="AU17" s="33">
+        <v>91</v>
+      </c>
       <c r="AV17" s="34"/>
       <c r="AW17" s="35"/>
-      <c r="AX17" s="36" t="str">
+      <c r="AX17" s="36">
         <f>IF(SUM(AU17:AW17)=0,"",ROUND(AVERAGE(AU17:AW17),0))</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="AY17" s="34">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="AZ17" s="34"/>
       <c r="BA17" s="35"/>
       <c r="BB17" s="37">
         <f>IF(SUM(AY17:BA17)=0,"",ROUND(AVERAGE(AY17:BA17),0))</f>
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="BC17" s="38">
-        <v>56.0</v>
+        <v>78.0</v>
       </c>
       <c r="BD17" s="39"/>
       <c r="BE17" s="40"/>
       <c r="BF17" s="41">
         <f>IF(SUM(F17,J17,N17,R17,V17,Z17,AD17,AH17,AL17,AP17,AT17,AX17,BB17)=0,"",ROUND(AVERAGE(F17,J17,N17,R17,V17,Z17,AD17,AH17,AL17,AP17,AT17,AX17,BB17),2))</f>
-        <v>72.9</v>
+        <v>92.64</v>
       </c>
       <c r="BG17" s="31">
         <v>10</v>
@@ -3895,31 +3918,31 @@
         <v>LEDEZMA ARAOZ IGNACIO</v>
       </c>
       <c r="BI17" s="44">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="BJ17" s="42"/>
       <c r="BK17" s="43"/>
       <c r="BL17" s="45">
         <f>IF(SUM(BI17:BK17)=0,"",ROUND(AVERAGE(BI17:BK17),0))</f>
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="BM17" s="44">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="BN17" s="42"/>
       <c r="BO17" s="43"/>
-      <c r="BP17" s="45" t="str">
+      <c r="BP17" s="45">
         <f>IF(SUM(BM17:BO17)=0,"",ROUND(AVERAGE(BM17:BO17),0))</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="BQ17" s="33">
-        <v>35.0</v>
+        <v>86.0</v>
       </c>
       <c r="BR17" s="34"/>
       <c r="BS17" s="35"/>
       <c r="BT17" s="36">
         <f>IF(SUM(BQ17:BS17)=0,"",ROUND(AVERAGE(BQ17:BS17),0))</f>
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -3930,17 +3953,17 @@
         <v>40</v>
       </c>
       <c r="C18" s="33">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" s="34"/>
       <c r="E18" s="35"/>
-      <c r="F18" s="36">
+      <c r="F18" s="36" t="str">
         <f>IF(SUM(C18:E18)=0,"",ROUND(AVERAGE(C18:E18),0))</f>
-        <v>65</v>
+        <v/>
       </c>
       <c r="G18" s="34">
         <f>IF(BQ18="","",BQ18)</f>
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H18" s="34" t="str">
         <f>IF(BR18="","",BR18)</f>
@@ -3952,52 +3975,52 @@
       </c>
       <c r="J18" s="37">
         <f>IF(BT18="","",BT18)</f>
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K18" s="33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35"/>
-      <c r="N18" s="36" t="str">
+      <c r="N18" s="36">
         <f>IF(SUM(K18:M18)=0,"",ROUND(AVERAGE(K18:M18),0))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="O18" s="34">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="P18" s="34"/>
       <c r="Q18" s="35"/>
       <c r="R18" s="37">
         <f>IF(SUM(O18:Q18)=0,"",ROUND(AVERAGE(O18:Q18),0))</f>
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="S18" s="33">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="T18" s="34"/>
       <c r="U18" s="35"/>
       <c r="V18" s="36">
         <f>IF(SUM(S18:U18)=0,"",ROUND(AVERAGE(S18:U18),0))</f>
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="W18" s="33">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="X18" s="34"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="36">
         <f>IF(SUM(W18:Y18)=0,"",ROUND(AVERAGE(W18:Y18),0))</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA18" s="34">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AB18" s="34"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="37">
         <f>IF(SUM(AA18:AC18)=0,"",ROUND(AVERAGE(AA18:AC18),0))</f>
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AE18" s="33"/>
       <c r="AF18" s="34"/>
@@ -4007,90 +4030,92 @@
         <v/>
       </c>
       <c r="AI18" s="33">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="AJ18" s="34"/>
       <c r="AK18" s="35"/>
       <c r="AL18" s="36">
         <f>IF(SUM(AI18:AK18)=0,"",ROUND(AVERAGE(AI18:AK18),0))</f>
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="AM18" s="33">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="AN18" s="34"/>
       <c r="AO18" s="35"/>
       <c r="AP18" s="36">
         <f>IF(SUM(AM18:AO18)=0,"",ROUND(AVERAGE(AM18:AO18),0))</f>
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="AQ18" s="33">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="AR18" s="34"/>
       <c r="AS18" s="35"/>
       <c r="AT18" s="36">
         <f>IF(SUM(AQ18:AS18)=0,"",ROUND(AVERAGE(AQ18:AS18),0))</f>
-        <v>62</v>
-      </c>
-      <c r="AU18" s="33"/>
+        <v>16</v>
+      </c>
+      <c r="AU18" s="33">
+        <v>15</v>
+      </c>
       <c r="AV18" s="34"/>
       <c r="AW18" s="35"/>
-      <c r="AX18" s="36" t="str">
+      <c r="AX18" s="36">
         <f>IF(SUM(AU18:AW18)=0,"",ROUND(AVERAGE(AU18:AW18),0))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="AY18" s="34">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AZ18" s="34"/>
       <c r="BA18" s="35"/>
       <c r="BB18" s="37">
         <f>IF(SUM(AY18:BA18)=0,"",ROUND(AVERAGE(AY18:BA18),0))</f>
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="BC18" s="38">
-        <v>47.0</v>
+        <v>30.0</v>
       </c>
       <c r="BD18" s="39"/>
       <c r="BE18" s="40"/>
       <c r="BF18" s="41">
         <f>IF(SUM(F18,J18,N18,R18,V18,Z18,AD18,AH18,AL18,AP18,AT18,AX18,BB18)=0,"",ROUND(AVERAGE(F18,J18,N18,R18,V18,Z18,AD18,AH18,AL18,AP18,AT18,AX18,BB18),2))</f>
-        <v>61.2</v>
+        <v>35.64</v>
       </c>
       <c r="BG18" s="31">
         <v>11</v>
       </c>
       <c r="BH18" s="32" t="str">
         <f>IF(B18="","",B18)</f>
-        <v>MARQUEZ VAN DER VEEN PEDRO</v>
+        <v>LONGPRE - KINGSTON BYRON</v>
       </c>
       <c r="BI18" s="44">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="BJ18" s="42"/>
       <c r="BK18" s="43"/>
       <c r="BL18" s="45">
         <f>IF(SUM(BI18:BK18)=0,"",ROUND(AVERAGE(BI18:BK18),0))</f>
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="BM18" s="44">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BN18" s="42"/>
       <c r="BO18" s="43"/>
-      <c r="BP18" s="45" t="str">
+      <c r="BP18" s="45">
         <f>IF(SUM(BM18:BO18)=0,"",ROUND(AVERAGE(BM18:BO18),0))</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="BQ18" s="33">
-        <v>35.0</v>
+        <v>22.0</v>
       </c>
       <c r="BR18" s="34"/>
       <c r="BS18" s="35"/>
       <c r="BT18" s="36">
         <f>IF(SUM(BQ18:BS18)=0,"",ROUND(AVERAGE(BQ18:BS18),0))</f>
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -4101,17 +4126,17 @@
         <v>41</v>
       </c>
       <c r="C19" s="33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D19" s="34"/>
       <c r="E19" s="35"/>
-      <c r="F19" s="36">
+      <c r="F19" s="36" t="str">
         <f>IF(SUM(C19:E19)=0,"",ROUND(AVERAGE(C19:E19),0))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="G19" s="34">
         <f>IF(BQ19="","",BQ19)</f>
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="H19" s="34" t="str">
         <f>IF(BR19="","",BR19)</f>
@@ -4123,52 +4148,52 @@
       </c>
       <c r="J19" s="37">
         <f>IF(BT19="","",BT19)</f>
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="K19" s="33">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="36" t="str">
+      <c r="N19" s="36">
         <f>IF(SUM(K19:M19)=0,"",ROUND(AVERAGE(K19:M19),0))</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="O19" s="34">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="P19" s="34"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="37">
         <f>IF(SUM(O19:Q19)=0,"",ROUND(AVERAGE(O19:Q19),0))</f>
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S19" s="33">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="T19" s="34"/>
       <c r="U19" s="35"/>
       <c r="V19" s="36">
         <f>IF(SUM(S19:U19)=0,"",ROUND(AVERAGE(S19:U19),0))</f>
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="W19" s="33">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="X19" s="34"/>
       <c r="Y19" s="35"/>
       <c r="Z19" s="36">
         <f>IF(SUM(W19:Y19)=0,"",ROUND(AVERAGE(W19:Y19),0))</f>
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="AA19" s="34">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="AB19" s="34"/>
       <c r="AC19" s="35"/>
       <c r="AD19" s="37">
         <f>IF(SUM(AA19:AC19)=0,"",ROUND(AVERAGE(AA19:AC19),0))</f>
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="AE19" s="33"/>
       <c r="AF19" s="34"/>
@@ -4178,90 +4203,92 @@
         <v/>
       </c>
       <c r="AI19" s="33">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="AJ19" s="34"/>
       <c r="AK19" s="35"/>
       <c r="AL19" s="36">
         <f>IF(SUM(AI19:AK19)=0,"",ROUND(AVERAGE(AI19:AK19),0))</f>
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="AM19" s="33">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AN19" s="34"/>
       <c r="AO19" s="35"/>
       <c r="AP19" s="36">
         <f>IF(SUM(AM19:AO19)=0,"",ROUND(AVERAGE(AM19:AO19),0))</f>
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AQ19" s="33">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="AR19" s="34"/>
       <c r="AS19" s="35"/>
       <c r="AT19" s="36">
         <f>IF(SUM(AQ19:AS19)=0,"",ROUND(AVERAGE(AQ19:AS19),0))</f>
-        <v>65</v>
-      </c>
-      <c r="AU19" s="33"/>
+        <v>86</v>
+      </c>
+      <c r="AU19" s="33">
+        <v>51</v>
+      </c>
       <c r="AV19" s="34"/>
       <c r="AW19" s="35"/>
-      <c r="AX19" s="36" t="str">
+      <c r="AX19" s="36">
         <f>IF(SUM(AU19:AW19)=0,"",ROUND(AVERAGE(AU19:AW19),0))</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="AY19" s="34">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="AZ19" s="34"/>
       <c r="BA19" s="35"/>
       <c r="BB19" s="37">
         <f>IF(SUM(AY19:BA19)=0,"",ROUND(AVERAGE(AY19:BA19),0))</f>
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="BC19" s="38">
-        <v>27.0</v>
+        <v>71.0</v>
       </c>
       <c r="BD19" s="39"/>
       <c r="BE19" s="40"/>
       <c r="BF19" s="41">
         <f>IF(SUM(F19,J19,N19,R19,V19,Z19,AD19,AH19,AL19,AP19,AT19,AX19,BB19)=0,"",ROUND(AVERAGE(F19,J19,N19,R19,V19,Z19,AD19,AH19,AL19,AP19,AT19,AX19,BB19),2))</f>
-        <v>35</v>
+        <v>84.36</v>
       </c>
       <c r="BG19" s="31">
         <v>12</v>
       </c>
       <c r="BH19" s="32" t="str">
         <f>IF(B19="","",B19)</f>
-        <v>ORGERO CAMPOS LEANDRO ANGELO</v>
+        <v>MARQUEZ VAN DER VEEN PEDRO</v>
       </c>
       <c r="BI19" s="44">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="BJ19" s="42"/>
       <c r="BK19" s="43"/>
       <c r="BL19" s="45">
         <f>IF(SUM(BI19:BK19)=0,"",ROUND(AVERAGE(BI19:BK19),0))</f>
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="BM19" s="44">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BN19" s="42"/>
       <c r="BO19" s="43"/>
-      <c r="BP19" s="45" t="str">
+      <c r="BP19" s="45">
         <f>IF(SUM(BM19:BO19)=0,"",ROUND(AVERAGE(BM19:BO19),0))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="BQ19" s="33">
-        <v>13.0</v>
+        <v>77.0</v>
       </c>
       <c r="BR19" s="34"/>
       <c r="BS19" s="35"/>
       <c r="BT19" s="36">
         <f>IF(SUM(BQ19:BS19)=0,"",ROUND(AVERAGE(BQ19:BS19),0))</f>
-        <v>13</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -4272,17 +4299,17 @@
         <v>42</v>
       </c>
       <c r="C20" s="33">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D20" s="34"/>
       <c r="E20" s="35"/>
-      <c r="F20" s="36">
+      <c r="F20" s="36" t="str">
         <f>IF(SUM(C20:E20)=0,"",ROUND(AVERAGE(C20:E20),0))</f>
-        <v>50</v>
+        <v/>
       </c>
       <c r="G20" s="34">
         <f>IF(BQ20="","",BQ20)</f>
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="H20" s="34" t="str">
         <f>IF(BR20="","",BR20)</f>
@@ -4294,52 +4321,52 @@
       </c>
       <c r="J20" s="37">
         <f>IF(BT20="","",BT20)</f>
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="K20" s="33">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="36" t="str">
+      <c r="N20" s="36">
         <f>IF(SUM(K20:M20)=0,"",ROUND(AVERAGE(K20:M20),0))</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="O20" s="34">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="P20" s="34"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="37">
         <f>IF(SUM(O20:Q20)=0,"",ROUND(AVERAGE(O20:Q20),0))</f>
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="S20" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="T20" s="34"/>
       <c r="U20" s="35"/>
       <c r="V20" s="36">
         <f>IF(SUM(S20:U20)=0,"",ROUND(AVERAGE(S20:U20),0))</f>
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="W20" s="33">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="X20" s="34"/>
       <c r="Y20" s="35"/>
       <c r="Z20" s="36">
         <f>IF(SUM(W20:Y20)=0,"",ROUND(AVERAGE(W20:Y20),0))</f>
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="AA20" s="34">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB20" s="34"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="37">
         <f>IF(SUM(AA20:AC20)=0,"",ROUND(AVERAGE(AA20:AC20),0))</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE20" s="33"/>
       <c r="AF20" s="34"/>
@@ -4349,90 +4376,92 @@
         <v/>
       </c>
       <c r="AI20" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="35"/>
       <c r="AL20" s="36">
         <f>IF(SUM(AI20:AK20)=0,"",ROUND(AVERAGE(AI20:AK20),0))</f>
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AM20" s="33">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AN20" s="34"/>
       <c r="AO20" s="35"/>
       <c r="AP20" s="36">
         <f>IF(SUM(AM20:AO20)=0,"",ROUND(AVERAGE(AM20:AO20),0))</f>
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AQ20" s="33">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="AR20" s="34"/>
       <c r="AS20" s="35"/>
       <c r="AT20" s="36">
         <f>IF(SUM(AQ20:AS20)=0,"",ROUND(AVERAGE(AQ20:AS20),0))</f>
-        <v>78</v>
-      </c>
-      <c r="AU20" s="33"/>
+        <v>67</v>
+      </c>
+      <c r="AU20" s="33">
+        <v>66</v>
+      </c>
       <c r="AV20" s="34"/>
       <c r="AW20" s="35"/>
-      <c r="AX20" s="36" t="str">
+      <c r="AX20" s="36">
         <f>IF(SUM(AU20:AW20)=0,"",ROUND(AVERAGE(AU20:AW20),0))</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="AY20" s="34">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AZ20" s="34"/>
       <c r="BA20" s="35"/>
       <c r="BB20" s="37">
         <f>IF(SUM(AY20:BA20)=0,"",ROUND(AVERAGE(AY20:BA20),0))</f>
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="BC20" s="38">
-        <v>49.0</v>
+        <v>62.0</v>
       </c>
       <c r="BD20" s="39"/>
       <c r="BE20" s="40"/>
       <c r="BF20" s="41">
         <f>IF(SUM(F20,J20,N20,R20,V20,Z20,AD20,AH20,AL20,AP20,AT20,AX20,BB20)=0,"",ROUND(AVERAGE(F20,J20,N20,R20,V20,Z20,AD20,AH20,AL20,AP20,AT20,AX20,BB20),2))</f>
-        <v>63.8</v>
+        <v>73.36</v>
       </c>
       <c r="BG20" s="31">
         <v>13</v>
       </c>
       <c r="BH20" s="32" t="str">
         <f>IF(B20="","",B20)</f>
-        <v>RAMALLO CAMPOS ABBY MICHELLE</v>
+        <v>ORGERO CAMPOS LEANDRO ANGELO</v>
       </c>
       <c r="BI20" s="44">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="BJ20" s="42"/>
       <c r="BK20" s="43"/>
       <c r="BL20" s="45">
         <f>IF(SUM(BI20:BK20)=0,"",ROUND(AVERAGE(BI20:BK20),0))</f>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="BM20" s="44">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="BN20" s="42"/>
       <c r="BO20" s="43"/>
-      <c r="BP20" s="45" t="str">
+      <c r="BP20" s="45">
         <f>IF(SUM(BM20:BO20)=0,"",ROUND(AVERAGE(BM20:BO20),0))</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="BQ20" s="33">
-        <v>34.0</v>
+        <v>72.0</v>
       </c>
       <c r="BR20" s="34"/>
       <c r="BS20" s="35"/>
       <c r="BT20" s="36">
         <f>IF(SUM(BQ20:BS20)=0,"",ROUND(AVERAGE(BQ20:BS20),0))</f>
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -4443,17 +4472,17 @@
         <v>43</v>
       </c>
       <c r="C21" s="33">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D21" s="34"/>
       <c r="E21" s="35"/>
-      <c r="F21" s="36">
+      <c r="F21" s="36" t="str">
         <f>IF(SUM(C21:E21)=0,"",ROUND(AVERAGE(C21:E21),0))</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="G21" s="34">
         <f>IF(BQ21="","",BQ21)</f>
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="H21" s="34" t="str">
         <f>IF(BR21="","",BR21)</f>
@@ -4465,52 +4494,52 @@
       </c>
       <c r="J21" s="37">
         <f>IF(BT21="","",BT21)</f>
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K21" s="33">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="36" t="str">
+      <c r="N21" s="36">
         <f>IF(SUM(K21:M21)=0,"",ROUND(AVERAGE(K21:M21),0))</f>
-        <v/>
+        <v>74</v>
       </c>
       <c r="O21" s="34">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="P21" s="34"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="37">
         <f>IF(SUM(O21:Q21)=0,"",ROUND(AVERAGE(O21:Q21),0))</f>
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="S21" s="33">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="T21" s="34"/>
       <c r="U21" s="35"/>
       <c r="V21" s="36">
         <f>IF(SUM(S21:U21)=0,"",ROUND(AVERAGE(S21:U21),0))</f>
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="W21" s="33">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="X21" s="34"/>
       <c r="Y21" s="35"/>
       <c r="Z21" s="36">
         <f>IF(SUM(W21:Y21)=0,"",ROUND(AVERAGE(W21:Y21),0))</f>
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="AA21" s="34">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AB21" s="34"/>
       <c r="AC21" s="35"/>
       <c r="AD21" s="37">
         <f>IF(SUM(AA21:AC21)=0,"",ROUND(AVERAGE(AA21:AC21),0))</f>
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AE21" s="33"/>
       <c r="AF21" s="34"/>
@@ -4520,90 +4549,92 @@
         <v/>
       </c>
       <c r="AI21" s="33">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="AJ21" s="34"/>
       <c r="AK21" s="35"/>
       <c r="AL21" s="36">
         <f>IF(SUM(AI21:AK21)=0,"",ROUND(AVERAGE(AI21:AK21),0))</f>
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="AM21" s="33">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="AN21" s="34"/>
       <c r="AO21" s="35"/>
       <c r="AP21" s="36">
         <f>IF(SUM(AM21:AO21)=0,"",ROUND(AVERAGE(AM21:AO21),0))</f>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="AQ21" s="33">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="AR21" s="34"/>
       <c r="AS21" s="35"/>
       <c r="AT21" s="36">
         <f>IF(SUM(AQ21:AS21)=0,"",ROUND(AVERAGE(AQ21:AS21),0))</f>
-        <v>33</v>
-      </c>
-      <c r="AU21" s="33"/>
+        <v>70</v>
+      </c>
+      <c r="AU21" s="33">
+        <v>91</v>
+      </c>
       <c r="AV21" s="34"/>
       <c r="AW21" s="35"/>
-      <c r="AX21" s="36" t="str">
+      <c r="AX21" s="36">
         <f>IF(SUM(AU21:AW21)=0,"",ROUND(AVERAGE(AU21:AW21),0))</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="AY21" s="34">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AZ21" s="34"/>
       <c r="BA21" s="35"/>
       <c r="BB21" s="37">
         <f>IF(SUM(AY21:BA21)=0,"",ROUND(AVERAGE(AY21:BA21),0))</f>
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="BC21" s="38">
-        <v>36.0</v>
+        <v>71.0</v>
       </c>
       <c r="BD21" s="39"/>
       <c r="BE21" s="40"/>
       <c r="BF21" s="41">
         <f>IF(SUM(F21,J21,N21,R21,V21,Z21,AD21,AH21,AL21,AP21,AT21,AX21,BB21)=0,"",ROUND(AVERAGE(F21,J21,N21,R21,V21,Z21,AD21,AH21,AL21,AP21,AT21,AX21,BB21),2))</f>
-        <v>47.1</v>
+        <v>83.73</v>
       </c>
       <c r="BG21" s="31">
         <v>14</v>
       </c>
       <c r="BH21" s="32" t="str">
         <f>IF(B21="","",B21)</f>
-        <v>SCIARAFFIA PERROGOND PIETRO ANDRES</v>
+        <v>RAMALLO CAMPOS ABBY MICHELLE</v>
       </c>
       <c r="BI21" s="44">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="BJ21" s="42"/>
       <c r="BK21" s="43"/>
       <c r="BL21" s="45">
         <f>IF(SUM(BI21:BK21)=0,"",ROUND(AVERAGE(BI21:BK21),0))</f>
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="BM21" s="44">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="BN21" s="42"/>
       <c r="BO21" s="43"/>
-      <c r="BP21" s="45" t="str">
+      <c r="BP21" s="45">
         <f>IF(SUM(BM21:BO21)=0,"",ROUND(AVERAGE(BM21:BO21),0))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="BQ21" s="33">
-        <v>18.0</v>
+        <v>85.0</v>
       </c>
       <c r="BR21" s="34"/>
       <c r="BS21" s="35"/>
       <c r="BT21" s="36">
         <f>IF(SUM(BQ21:BS21)=0,"",ROUND(AVERAGE(BQ21:BS21),0))</f>
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -4614,17 +4645,17 @@
         <v>44</v>
       </c>
       <c r="C22" s="33">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D22" s="34"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="36">
+      <c r="F22" s="36" t="str">
         <f>IF(SUM(C22:E22)=0,"",ROUND(AVERAGE(C22:E22),0))</f>
-        <v>65</v>
+        <v/>
       </c>
       <c r="G22" s="34">
         <f>IF(BQ22="","",BQ22)</f>
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="H22" s="34" t="str">
         <f>IF(BR22="","",BR22)</f>
@@ -4636,52 +4667,52 @@
       </c>
       <c r="J22" s="37">
         <f>IF(BT22="","",BT22)</f>
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="K22" s="33">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="36" t="str">
+      <c r="N22" s="36">
         <f>IF(SUM(K22:M22)=0,"",ROUND(AVERAGE(K22:M22),0))</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="O22" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P22" s="34"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="37">
         <f>IF(SUM(O22:Q22)=0,"",ROUND(AVERAGE(O22:Q22),0))</f>
+        <v>81</v>
+      </c>
+      <c r="S22" s="33">
         <v>82</v>
-      </c>
-      <c r="S22" s="33">
-        <v>77</v>
       </c>
       <c r="T22" s="34"/>
       <c r="U22" s="35"/>
       <c r="V22" s="36">
         <f>IF(SUM(S22:U22)=0,"",ROUND(AVERAGE(S22:U22),0))</f>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="W22" s="33">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="X22" s="34"/>
       <c r="Y22" s="35"/>
       <c r="Z22" s="36">
         <f>IF(SUM(W22:Y22)=0,"",ROUND(AVERAGE(W22:Y22),0))</f>
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="AA22" s="34">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AB22" s="34"/>
       <c r="AC22" s="35"/>
       <c r="AD22" s="37">
         <f>IF(SUM(AA22:AC22)=0,"",ROUND(AVERAGE(AA22:AC22),0))</f>
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AE22" s="33"/>
       <c r="AF22" s="34"/>
@@ -4691,90 +4722,92 @@
         <v/>
       </c>
       <c r="AI22" s="33">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="AJ22" s="34"/>
       <c r="AK22" s="35"/>
       <c r="AL22" s="36">
         <f>IF(SUM(AI22:AK22)=0,"",ROUND(AVERAGE(AI22:AK22),0))</f>
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="AM22" s="33">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AN22" s="34"/>
       <c r="AO22" s="35"/>
       <c r="AP22" s="36">
         <f>IF(SUM(AM22:AO22)=0,"",ROUND(AVERAGE(AM22:AO22),0))</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AQ22" s="33">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AR22" s="34"/>
       <c r="AS22" s="35"/>
       <c r="AT22" s="36">
         <f>IF(SUM(AQ22:AS22)=0,"",ROUND(AVERAGE(AQ22:AS22),0))</f>
-        <v>71</v>
-      </c>
-      <c r="AU22" s="33"/>
+        <v>83</v>
+      </c>
+      <c r="AU22" s="33">
+        <v>51</v>
+      </c>
       <c r="AV22" s="34"/>
       <c r="AW22" s="35"/>
-      <c r="AX22" s="36" t="str">
+      <c r="AX22" s="36">
         <f>IF(SUM(AU22:AW22)=0,"",ROUND(AVERAGE(AU22:AW22),0))</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="AY22" s="34">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="AZ22" s="34"/>
       <c r="BA22" s="35"/>
       <c r="BB22" s="37">
         <f>IF(SUM(AY22:BA22)=0,"",ROUND(AVERAGE(AY22:BA22),0))</f>
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="BC22" s="38">
-        <v>48.0</v>
+        <v>65.0</v>
       </c>
       <c r="BD22" s="39"/>
       <c r="BE22" s="40"/>
       <c r="BF22" s="41">
         <f>IF(SUM(F22,J22,N22,R22,V22,Z22,AD22,AH22,AL22,AP22,AT22,AX22,BB22)=0,"",ROUND(AVERAGE(F22,J22,N22,R22,V22,Z22,AD22,AH22,AL22,AP22,AT22,AX22,BB22),2))</f>
-        <v>62.7</v>
+        <v>76.64</v>
       </c>
       <c r="BG22" s="31">
         <v>15</v>
       </c>
       <c r="BH22" s="32" t="str">
         <f>IF(B22="","",B22)</f>
-        <v>SMULDERS CHAMBI ISABELLA VICTORIA</v>
+        <v>SCIARAFFIA PERROGOND PIETRO ANDRES</v>
       </c>
       <c r="BI22" s="44">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BJ22" s="42"/>
       <c r="BK22" s="43"/>
       <c r="BL22" s="45">
         <f>IF(SUM(BI22:BK22)=0,"",ROUND(AVERAGE(BI22:BK22),0))</f>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BM22" s="44">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="BN22" s="42"/>
       <c r="BO22" s="43"/>
-      <c r="BP22" s="45" t="str">
+      <c r="BP22" s="45">
         <f>IF(SUM(BM22:BO22)=0,"",ROUND(AVERAGE(BM22:BO22),0))</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="BQ22" s="33">
-        <v>35.0</v>
+        <v>69.0</v>
       </c>
       <c r="BR22" s="34"/>
       <c r="BS22" s="35"/>
       <c r="BT22" s="36">
         <f>IF(SUM(BQ22:BS22)=0,"",ROUND(AVERAGE(BQ22:BS22),0))</f>
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -4785,17 +4818,17 @@
         <v>45</v>
       </c>
       <c r="C23" s="33">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D23" s="34"/>
       <c r="E23" s="35"/>
-      <c r="F23" s="36">
+      <c r="F23" s="36" t="str">
         <f>IF(SUM(C23:E23)=0,"",ROUND(AVERAGE(C23:E23),0))</f>
-        <v>42</v>
+        <v/>
       </c>
       <c r="G23" s="34">
         <f>IF(BQ23="","",BQ23)</f>
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="H23" s="34" t="str">
         <f>IF(BR23="","",BR23)</f>
@@ -4807,52 +4840,52 @@
       </c>
       <c r="J23" s="37">
         <f>IF(BT23="","",BT23)</f>
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="K23" s="33">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="36" t="str">
+      <c r="N23" s="36">
         <f>IF(SUM(K23:M23)=0,"",ROUND(AVERAGE(K23:M23),0))</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="O23" s="34">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="37">
         <f>IF(SUM(O23:Q23)=0,"",ROUND(AVERAGE(O23:Q23),0))</f>
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="S23" s="33">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="T23" s="34"/>
       <c r="U23" s="35"/>
       <c r="V23" s="36">
         <f>IF(SUM(S23:U23)=0,"",ROUND(AVERAGE(S23:U23),0))</f>
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="W23" s="33">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="X23" s="34"/>
       <c r="Y23" s="35"/>
       <c r="Z23" s="36">
         <f>IF(SUM(W23:Y23)=0,"",ROUND(AVERAGE(W23:Y23),0))</f>
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="AA23" s="34">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="AB23" s="34"/>
       <c r="AC23" s="35"/>
       <c r="AD23" s="37">
         <f>IF(SUM(AA23:AC23)=0,"",ROUND(AVERAGE(AA23:AC23),0))</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="AE23" s="33"/>
       <c r="AF23" s="34"/>
@@ -4862,90 +4895,92 @@
         <v/>
       </c>
       <c r="AI23" s="33">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AJ23" s="34"/>
       <c r="AK23" s="35"/>
       <c r="AL23" s="36">
         <f>IF(SUM(AI23:AK23)=0,"",ROUND(AVERAGE(AI23:AK23),0))</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AM23" s="33">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="AN23" s="34"/>
       <c r="AO23" s="35"/>
       <c r="AP23" s="36">
         <f>IF(SUM(AM23:AO23)=0,"",ROUND(AVERAGE(AM23:AO23),0))</f>
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="AQ23" s="33">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="AR23" s="34"/>
       <c r="AS23" s="35"/>
       <c r="AT23" s="36">
         <f>IF(SUM(AQ23:AS23)=0,"",ROUND(AVERAGE(AQ23:AS23),0))</f>
-        <v>68</v>
-      </c>
-      <c r="AU23" s="33"/>
+        <v>51</v>
+      </c>
+      <c r="AU23" s="33">
+        <v>59</v>
+      </c>
       <c r="AV23" s="34"/>
       <c r="AW23" s="35"/>
-      <c r="AX23" s="36" t="str">
+      <c r="AX23" s="36">
         <f>IF(SUM(AU23:AW23)=0,"",ROUND(AVERAGE(AU23:AW23),0))</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="AY23" s="34">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="AZ23" s="34"/>
       <c r="BA23" s="35"/>
       <c r="BB23" s="37">
         <f>IF(SUM(AY23:BA23)=0,"",ROUND(AVERAGE(AY23:BA23),0))</f>
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="BC23" s="38">
-        <v>46.0</v>
+        <v>59.0</v>
       </c>
       <c r="BD23" s="39"/>
       <c r="BE23" s="40"/>
       <c r="BF23" s="41">
         <f>IF(SUM(F23,J23,N23,R23,V23,Z23,AD23,AH23,AL23,AP23,AT23,AX23,BB23)=0,"",ROUND(AVERAGE(F23,J23,N23,R23,V23,Z23,AD23,AH23,AL23,AP23,AT23,AX23,BB23),2))</f>
-        <v>59.4</v>
+        <v>69.45</v>
       </c>
       <c r="BG23" s="31">
         <v>16</v>
       </c>
       <c r="BH23" s="32" t="str">
         <f>IF(B23="","",B23)</f>
-        <v>TAPIA ORIHUELA MATIAS</v>
+        <v>SMULDERS CHAMBI ISABELLA VICTORIA</v>
       </c>
       <c r="BI23" s="44">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="BJ23" s="42"/>
       <c r="BK23" s="43"/>
       <c r="BL23" s="45">
         <f>IF(SUM(BI23:BK23)=0,"",ROUND(AVERAGE(BI23:BK23),0))</f>
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="BM23" s="44">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BN23" s="42"/>
       <c r="BO23" s="43"/>
-      <c r="BP23" s="45" t="str">
+      <c r="BP23" s="45">
         <f>IF(SUM(BM23:BO23)=0,"",ROUND(AVERAGE(BM23:BO23),0))</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="BQ23" s="33">
-        <v>26.0</v>
+        <v>77.0</v>
       </c>
       <c r="BR23" s="34"/>
       <c r="BS23" s="35"/>
       <c r="BT23" s="36">
         <f>IF(SUM(BQ23:BS23)=0,"",ROUND(AVERAGE(BQ23:BS23),0))</f>
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -4956,17 +4991,17 @@
         <v>46</v>
       </c>
       <c r="C24" s="33">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D24" s="34"/>
       <c r="E24" s="35"/>
-      <c r="F24" s="36">
+      <c r="F24" s="36" t="str">
         <f>IF(SUM(C24:E24)=0,"",ROUND(AVERAGE(C24:E24),0))</f>
-        <v>58</v>
+        <v/>
       </c>
       <c r="G24" s="34">
         <f>IF(BQ24="","",BQ24)</f>
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="H24" s="34" t="str">
         <f>IF(BR24="","",BR24)</f>
@@ -4978,52 +5013,52 @@
       </c>
       <c r="J24" s="37">
         <f>IF(BT24="","",BT24)</f>
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="K24" s="33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35"/>
-      <c r="N24" s="36" t="str">
+      <c r="N24" s="36">
         <f>IF(SUM(K24:M24)=0,"",ROUND(AVERAGE(K24:M24),0))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O24" s="34">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="37">
         <f>IF(SUM(O24:Q24)=0,"",ROUND(AVERAGE(O24:Q24),0))</f>
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="S24" s="33">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T24" s="34"/>
       <c r="U24" s="35"/>
       <c r="V24" s="36">
         <f>IF(SUM(S24:U24)=0,"",ROUND(AVERAGE(S24:U24),0))</f>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="W24" s="33">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="X24" s="34"/>
       <c r="Y24" s="35"/>
       <c r="Z24" s="36">
         <f>IF(SUM(W24:Y24)=0,"",ROUND(AVERAGE(W24:Y24),0))</f>
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AA24" s="34">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AB24" s="34"/>
       <c r="AC24" s="35"/>
       <c r="AD24" s="37">
         <f>IF(SUM(AA24:AC24)=0,"",ROUND(AVERAGE(AA24:AC24),0))</f>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AE24" s="33"/>
       <c r="AF24" s="34"/>
@@ -5033,90 +5068,92 @@
         <v/>
       </c>
       <c r="AI24" s="33">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AJ24" s="34"/>
       <c r="AK24" s="35"/>
       <c r="AL24" s="36">
         <f>IF(SUM(AI24:AK24)=0,"",ROUND(AVERAGE(AI24:AK24),0))</f>
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AM24" s="33">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="AN24" s="34"/>
       <c r="AO24" s="35"/>
       <c r="AP24" s="36">
         <f>IF(SUM(AM24:AO24)=0,"",ROUND(AVERAGE(AM24:AO24),0))</f>
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="AQ24" s="33">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="AR24" s="34"/>
       <c r="AS24" s="35"/>
       <c r="AT24" s="36">
         <f>IF(SUM(AQ24:AS24)=0,"",ROUND(AVERAGE(AQ24:AS24),0))</f>
-        <v>41</v>
-      </c>
-      <c r="AU24" s="33"/>
+        <v>85</v>
+      </c>
+      <c r="AU24" s="33">
+        <v>56</v>
+      </c>
       <c r="AV24" s="34"/>
       <c r="AW24" s="35"/>
-      <c r="AX24" s="36" t="str">
+      <c r="AX24" s="36">
         <f>IF(SUM(AU24:AW24)=0,"",ROUND(AVERAGE(AU24:AW24),0))</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="AY24" s="34">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AZ24" s="34"/>
       <c r="BA24" s="35"/>
       <c r="BB24" s="37">
         <f>IF(SUM(AY24:BA24)=0,"",ROUND(AVERAGE(AY24:BA24),0))</f>
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="BC24" s="38">
-        <v>44.0</v>
+        <v>69.0</v>
       </c>
       <c r="BD24" s="39"/>
       <c r="BE24" s="40"/>
       <c r="BF24" s="41">
         <f>IF(SUM(F24,J24,N24,R24,V24,Z24,AD24,AH24,AL24,AP24,AT24,AX24,BB24)=0,"",ROUND(AVERAGE(F24,J24,N24,R24,V24,Z24,AD24,AH24,AL24,AP24,AT24,AX24,BB24),2))</f>
-        <v>56.9</v>
+        <v>81.27</v>
       </c>
       <c r="BG24" s="31">
         <v>17</v>
       </c>
       <c r="BH24" s="32" t="str">
         <f>IF(B24="","",B24)</f>
-        <v>TORRELIO GAMARRA DEREK ADRIANO</v>
+        <v>TAPIA ORIHUELA MATIAS</v>
       </c>
       <c r="BI24" s="44">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="BJ24" s="42"/>
       <c r="BK24" s="43"/>
       <c r="BL24" s="45">
         <f>IF(SUM(BI24:BK24)=0,"",ROUND(AVERAGE(BI24:BK24),0))</f>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="BM24" s="44">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="BN24" s="42"/>
       <c r="BO24" s="43"/>
-      <c r="BP24" s="45" t="str">
+      <c r="BP24" s="45">
         <f>IF(SUM(BM24:BO24)=0,"",ROUND(AVERAGE(BM24:BO24),0))</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="BQ24" s="33">
-        <v>37.0</v>
+        <v>75.0</v>
       </c>
       <c r="BR24" s="34"/>
       <c r="BS24" s="35"/>
       <c r="BT24" s="36">
         <f>IF(SUM(BQ24:BS24)=0,"",ROUND(AVERAGE(BQ24:BS24),0))</f>
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -5127,17 +5164,17 @@
         <v>47</v>
       </c>
       <c r="C25" s="33">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D25" s="34"/>
       <c r="E25" s="35"/>
-      <c r="F25" s="36">
+      <c r="F25" s="36" t="str">
         <f>IF(SUM(C25:E25)=0,"",ROUND(AVERAGE(C25:E25),0))</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="G25" s="34">
         <f>IF(BQ25="","",BQ25)</f>
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="H25" s="34" t="str">
         <f>IF(BR25="","",BR25)</f>
@@ -5149,52 +5186,52 @@
       </c>
       <c r="J25" s="37">
         <f>IF(BT25="","",BT25)</f>
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="K25" s="33">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35"/>
-      <c r="N25" s="36" t="str">
+      <c r="N25" s="36">
         <f>IF(SUM(K25:M25)=0,"",ROUND(AVERAGE(K25:M25),0))</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="O25" s="34">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="37">
         <f>IF(SUM(O25:Q25)=0,"",ROUND(AVERAGE(O25:Q25),0))</f>
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="S25" s="33">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="T25" s="34"/>
       <c r="U25" s="35"/>
       <c r="V25" s="36">
         <f>IF(SUM(S25:U25)=0,"",ROUND(AVERAGE(S25:U25),0))</f>
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="W25" s="33">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="X25" s="34"/>
       <c r="Y25" s="35"/>
       <c r="Z25" s="36">
         <f>IF(SUM(W25:Y25)=0,"",ROUND(AVERAGE(W25:Y25),0))</f>
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA25" s="34">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="AB25" s="34"/>
       <c r="AC25" s="35"/>
       <c r="AD25" s="37">
         <f>IF(SUM(AA25:AC25)=0,"",ROUND(AVERAGE(AA25:AC25),0))</f>
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="AE25" s="33"/>
       <c r="AF25" s="34"/>
@@ -5204,90 +5241,92 @@
         <v/>
       </c>
       <c r="AI25" s="33">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="AJ25" s="34"/>
       <c r="AK25" s="35"/>
       <c r="AL25" s="36">
         <f>IF(SUM(AI25:AK25)=0,"",ROUND(AVERAGE(AI25:AK25),0))</f>
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="AM25" s="33">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AN25" s="34"/>
       <c r="AO25" s="35"/>
       <c r="AP25" s="36">
         <f>IF(SUM(AM25:AO25)=0,"",ROUND(AVERAGE(AM25:AO25),0))</f>
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AQ25" s="33">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AR25" s="34"/>
       <c r="AS25" s="35"/>
       <c r="AT25" s="36">
         <f>IF(SUM(AQ25:AS25)=0,"",ROUND(AVERAGE(AQ25:AS25),0))</f>
-        <v>83</v>
-      </c>
-      <c r="AU25" s="33"/>
+        <v>65</v>
+      </c>
+      <c r="AU25" s="33">
+        <v>91</v>
+      </c>
       <c r="AV25" s="34"/>
       <c r="AW25" s="35"/>
-      <c r="AX25" s="36" t="str">
+      <c r="AX25" s="36">
         <f>IF(SUM(AU25:AW25)=0,"",ROUND(AVERAGE(AU25:AW25),0))</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="AY25" s="34">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="AZ25" s="34"/>
       <c r="BA25" s="35"/>
       <c r="BB25" s="37">
         <f>IF(SUM(AY25:BA25)=0,"",ROUND(AVERAGE(AY25:BA25),0))</f>
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="BC25" s="38">
-        <v>37.0</v>
+        <v>70.0</v>
       </c>
       <c r="BD25" s="39"/>
       <c r="BE25" s="40"/>
       <c r="BF25" s="41">
         <f>IF(SUM(F25,J25,N25,R25,V25,Z25,AD25,AH25,AL25,AP25,AT25,AX25,BB25)=0,"",ROUND(AVERAGE(F25,J25,N25,R25,V25,Z25,AD25,AH25,AL25,AP25,AT25,AX25,BB25),2))</f>
-        <v>48.1</v>
+        <v>83</v>
       </c>
       <c r="BG25" s="31">
         <v>18</v>
       </c>
       <c r="BH25" s="32" t="str">
         <f>IF(B25="","",B25)</f>
-        <v>TRIGO ZAMBRANA ARIANA</v>
+        <v>TORRELIO GAMARRA DEREK ADRIANO</v>
       </c>
       <c r="BI25" s="44">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="BJ25" s="42"/>
       <c r="BK25" s="43"/>
       <c r="BL25" s="45">
         <f>IF(SUM(BI25:BK25)=0,"",ROUND(AVERAGE(BI25:BK25),0))</f>
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="BM25" s="44">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BN25" s="42"/>
       <c r="BO25" s="43"/>
-      <c r="BP25" s="45" t="str">
+      <c r="BP25" s="45">
         <f>IF(SUM(BM25:BO25)=0,"",ROUND(AVERAGE(BM25:BO25),0))</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="BQ25" s="33">
-        <v>29.0</v>
+        <v>88.0</v>
       </c>
       <c r="BR25" s="34"/>
       <c r="BS25" s="35"/>
       <c r="BT25" s="36">
         <f>IF(SUM(BQ25:BS25)=0,"",ROUND(AVERAGE(BQ25:BS25),0))</f>
-        <v>29</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -5298,17 +5337,17 @@
         <v>48</v>
       </c>
       <c r="C26" s="33">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D26" s="34"/>
       <c r="E26" s="35"/>
-      <c r="F26" s="36">
+      <c r="F26" s="36" t="str">
         <f>IF(SUM(C26:E26)=0,"",ROUND(AVERAGE(C26:E26),0))</f>
-        <v>56</v>
+        <v/>
       </c>
       <c r="G26" s="34">
         <f>IF(BQ26="","",BQ26)</f>
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="H26" s="34" t="str">
         <f>IF(BR26="","",BR26)</f>
@@ -5320,25 +5359,25 @@
       </c>
       <c r="J26" s="37">
         <f>IF(BT26="","",BT26)</f>
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="K26" s="33">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35"/>
-      <c r="N26" s="36" t="str">
+      <c r="N26" s="36">
         <f>IF(SUM(K26:M26)=0,"",ROUND(AVERAGE(K26:M26),0))</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="O26" s="34">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="P26" s="34"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="37">
         <f>IF(SUM(O26:Q26)=0,"",ROUND(AVERAGE(O26:Q26),0))</f>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="S26" s="33">
         <v>85</v>
@@ -5350,22 +5389,22 @@
         <v>85</v>
       </c>
       <c r="W26" s="33">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="X26" s="34"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="36">
         <f>IF(SUM(W26:Y26)=0,"",ROUND(AVERAGE(W26:Y26),0))</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AA26" s="34">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AB26" s="34"/>
       <c r="AC26" s="35"/>
       <c r="AD26" s="37">
         <f>IF(SUM(AA26:AC26)=0,"",ROUND(AVERAGE(AA26:AC26),0))</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AE26" s="33"/>
       <c r="AF26" s="34"/>
@@ -5375,90 +5414,92 @@
         <v/>
       </c>
       <c r="AI26" s="33">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="AJ26" s="34"/>
       <c r="AK26" s="35"/>
       <c r="AL26" s="36">
         <f>IF(SUM(AI26:AK26)=0,"",ROUND(AVERAGE(AI26:AK26),0))</f>
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="AM26" s="33">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="AN26" s="34"/>
       <c r="AO26" s="35"/>
       <c r="AP26" s="36">
         <f>IF(SUM(AM26:AO26)=0,"",ROUND(AVERAGE(AM26:AO26),0))</f>
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="AQ26" s="33">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AR26" s="34"/>
       <c r="AS26" s="35"/>
       <c r="AT26" s="36">
         <f>IF(SUM(AQ26:AS26)=0,"",ROUND(AVERAGE(AQ26:AS26),0))</f>
-        <v>49</v>
-      </c>
-      <c r="AU26" s="33"/>
+        <v>56</v>
+      </c>
+      <c r="AU26" s="33">
+        <v>60</v>
+      </c>
       <c r="AV26" s="34"/>
       <c r="AW26" s="35"/>
-      <c r="AX26" s="36" t="str">
+      <c r="AX26" s="36">
         <f>IF(SUM(AU26:AW26)=0,"",ROUND(AVERAGE(AU26:AW26),0))</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="AY26" s="34">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="AZ26" s="34"/>
       <c r="BA26" s="35"/>
       <c r="BB26" s="37">
         <f>IF(SUM(AY26:BA26)=0,"",ROUND(AVERAGE(AY26:BA26),0))</f>
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="BC26" s="38">
-        <v>51.0</v>
+        <v>60.0</v>
       </c>
       <c r="BD26" s="39"/>
       <c r="BE26" s="40"/>
       <c r="BF26" s="41">
         <f>IF(SUM(F26,J26,N26,R26,V26,Z26,AD26,AH26,AL26,AP26,AT26,AX26,BB26)=0,"",ROUND(AVERAGE(F26,J26,N26,R26,V26,Z26,AD26,AH26,AL26,AP26,AT26,AX26,BB26),2))</f>
-        <v>66.4</v>
+        <v>70.55</v>
       </c>
       <c r="BG26" s="31">
         <v>19</v>
       </c>
       <c r="BH26" s="46" t="str">
         <f>IF(B26="","",B26)</f>
-        <v>URIONA SEJAS JUAN ANDRES</v>
+        <v>TRIGO ZAMBRANA ARIANA</v>
       </c>
       <c r="BI26" s="44">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="BJ26" s="42"/>
       <c r="BK26" s="43"/>
       <c r="BL26" s="45">
         <f>IF(SUM(BI26:BK26)=0,"",ROUND(AVERAGE(BI26:BK26),0))</f>
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="BM26" s="44">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BN26" s="42"/>
       <c r="BO26" s="43"/>
-      <c r="BP26" s="45" t="str">
+      <c r="BP26" s="45">
         <f>IF(SUM(BM26:BO26)=0,"",ROUND(AVERAGE(BM26:BO26),0))</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="BQ26" s="33">
-        <v>36.0</v>
+        <v>75.0</v>
       </c>
       <c r="BR26" s="34"/>
       <c r="BS26" s="35"/>
       <c r="BT26" s="36">
         <f>IF(SUM(BQ26:BS26)=0,"",ROUND(AVERAGE(BQ26:BS26),0))</f>
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -5469,17 +5510,17 @@
         <v>49</v>
       </c>
       <c r="C27" s="33">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D27" s="34"/>
       <c r="E27" s="35"/>
-      <c r="F27" s="36">
+      <c r="F27" s="36" t="str">
         <f>IF(SUM(C27:E27)=0,"",ROUND(AVERAGE(C27:E27),0))</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="G27" s="34">
         <f>IF(BQ27="","",BQ27)</f>
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="H27" s="34" t="str">
         <f>IF(BR27="","",BR27)</f>
@@ -5491,52 +5532,52 @@
       </c>
       <c r="J27" s="37">
         <f>IF(BT27="","",BT27)</f>
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="K27" s="33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35"/>
-      <c r="N27" s="36" t="str">
+      <c r="N27" s="36">
         <f>IF(SUM(K27:M27)=0,"",ROUND(AVERAGE(K27:M27),0))</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="O27" s="34">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="P27" s="34"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="37">
         <f>IF(SUM(O27:Q27)=0,"",ROUND(AVERAGE(O27:Q27),0))</f>
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="S27" s="33">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="T27" s="34"/>
       <c r="U27" s="35"/>
       <c r="V27" s="36">
         <f>IF(SUM(S27:U27)=0,"",ROUND(AVERAGE(S27:U27),0))</f>
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="W27" s="33">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="X27" s="34"/>
       <c r="Y27" s="35"/>
       <c r="Z27" s="36">
         <f>IF(SUM(W27:Y27)=0,"",ROUND(AVERAGE(W27:Y27),0))</f>
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="34">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB27" s="34"/>
       <c r="AC27" s="35"/>
       <c r="AD27" s="37">
         <f>IF(SUM(AA27:AC27)=0,"",ROUND(AVERAGE(AA27:AC27),0))</f>
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AE27" s="33"/>
       <c r="AF27" s="34"/>
@@ -5546,90 +5587,92 @@
         <v/>
       </c>
       <c r="AI27" s="33">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="AJ27" s="34"/>
       <c r="AK27" s="35"/>
       <c r="AL27" s="36">
         <f>IF(SUM(AI27:AK27)=0,"",ROUND(AVERAGE(AI27:AK27),0))</f>
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="AM27" s="33">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AN27" s="34"/>
       <c r="AO27" s="35"/>
       <c r="AP27" s="36">
         <f>IF(SUM(AM27:AO27)=0,"",ROUND(AVERAGE(AM27:AO27),0))</f>
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AQ27" s="33">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AR27" s="34"/>
       <c r="AS27" s="35"/>
       <c r="AT27" s="36">
         <f>IF(SUM(AQ27:AS27)=0,"",ROUND(AVERAGE(AQ27:AS27),0))</f>
-        <v>78</v>
-      </c>
-      <c r="AU27" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="AU27" s="33">
+        <v>89</v>
+      </c>
       <c r="AV27" s="34"/>
       <c r="AW27" s="35"/>
-      <c r="AX27" s="36" t="str">
+      <c r="AX27" s="36">
         <f>IF(SUM(AU27:AW27)=0,"",ROUND(AVERAGE(AU27:AW27),0))</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="AY27" s="34">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AZ27" s="34"/>
       <c r="BA27" s="35"/>
       <c r="BB27" s="37">
         <f>IF(SUM(AY27:BA27)=0,"",ROUND(AVERAGE(AY27:BA27),0))</f>
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BC27" s="38">
-        <v>40.0</v>
+        <v>80.0</v>
       </c>
       <c r="BD27" s="39"/>
       <c r="BE27" s="40"/>
       <c r="BF27" s="41">
         <f>IF(SUM(F27,J27,N27,R27,V27,Z27,AD27,AH27,AL27,AP27,AT27,AX27,BB27)=0,"",ROUND(AVERAGE(F27,J27,N27,R27,V27,Z27,AD27,AH27,AL27,AP27,AT27,AX27,BB27),2))</f>
-        <v>52</v>
+        <v>94.09</v>
       </c>
       <c r="BG27" s="31">
         <v>20</v>
       </c>
       <c r="BH27" s="32" t="str">
         <f>IF(B27="","",B27)</f>
-        <v>VARGAS MENDIETA FABRICIO</v>
+        <v>URIONA SEJAS JUAN ANDRES</v>
       </c>
       <c r="BI27" s="44">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="BJ27" s="42"/>
       <c r="BK27" s="43"/>
       <c r="BL27" s="45">
         <f>IF(SUM(BI27:BK27)=0,"",ROUND(AVERAGE(BI27:BK27),0))</f>
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="BM27" s="44">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BN27" s="42"/>
       <c r="BO27" s="43"/>
-      <c r="BP27" s="45" t="str">
+      <c r="BP27" s="45">
         <f>IF(SUM(BM27:BO27)=0,"",ROUND(AVERAGE(BM27:BO27),0))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="BQ27" s="33">
-        <v>27.0</v>
+        <v>84.0</v>
       </c>
       <c r="BR27" s="34"/>
       <c r="BS27" s="35"/>
       <c r="BT27" s="36">
         <f>IF(SUM(BQ27:BS27)=0,"",ROUND(AVERAGE(BQ27:BS27),0))</f>
-        <v>27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -5640,17 +5683,17 @@
         <v>50</v>
       </c>
       <c r="C28" s="33">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D28" s="34"/>
       <c r="E28" s="35"/>
-      <c r="F28" s="36">
+      <c r="F28" s="36" t="str">
         <f>IF(SUM(C28:E28)=0,"",ROUND(AVERAGE(C28:E28),0))</f>
-        <v>66</v>
+        <v/>
       </c>
       <c r="G28" s="34">
         <f>IF(BQ28="","",BQ28)</f>
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H28" s="34" t="str">
         <f>IF(BR28="","",BR28)</f>
@@ -5662,52 +5705,52 @@
       </c>
       <c r="J28" s="37">
         <f>IF(BT28="","",BT28)</f>
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="K28" s="33">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="35"/>
-      <c r="N28" s="36" t="str">
+      <c r="N28" s="36">
         <f>IF(SUM(K28:M28)=0,"",ROUND(AVERAGE(K28:M28),0))</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="O28" s="34">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="P28" s="34"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="37">
         <f>IF(SUM(O28:Q28)=0,"",ROUND(AVERAGE(O28:Q28),0))</f>
+        <v>93</v>
+      </c>
+      <c r="S28" s="33">
         <v>79</v>
-      </c>
-      <c r="S28" s="33">
-        <v>41</v>
       </c>
       <c r="T28" s="34"/>
       <c r="U28" s="35"/>
       <c r="V28" s="36">
         <f>IF(SUM(S28:U28)=0,"",ROUND(AVERAGE(S28:U28),0))</f>
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="W28" s="33">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="X28" s="34"/>
       <c r="Y28" s="35"/>
       <c r="Z28" s="36">
         <f>IF(SUM(W28:Y28)=0,"",ROUND(AVERAGE(W28:Y28),0))</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AA28" s="34">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AB28" s="34"/>
       <c r="AC28" s="35"/>
       <c r="AD28" s="37">
         <f>IF(SUM(AA28:AC28)=0,"",ROUND(AVERAGE(AA28:AC28),0))</f>
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AE28" s="33"/>
       <c r="AF28" s="34"/>
@@ -5717,90 +5760,92 @@
         <v/>
       </c>
       <c r="AI28" s="33">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="AJ28" s="34"/>
       <c r="AK28" s="35"/>
       <c r="AL28" s="36">
         <f>IF(SUM(AI28:AK28)=0,"",ROUND(AVERAGE(AI28:AK28),0))</f>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="AM28" s="33">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="AN28" s="34"/>
       <c r="AO28" s="35"/>
       <c r="AP28" s="36">
         <f>IF(SUM(AM28:AO28)=0,"",ROUND(AVERAGE(AM28:AO28),0))</f>
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="AQ28" s="33">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="AR28" s="34"/>
       <c r="AS28" s="35"/>
       <c r="AT28" s="36">
         <f>IF(SUM(AQ28:AS28)=0,"",ROUND(AVERAGE(AQ28:AS28),0))</f>
-        <v>78</v>
-      </c>
-      <c r="AU28" s="33"/>
+        <v>54</v>
+      </c>
+      <c r="AU28" s="33">
+        <v>53</v>
+      </c>
       <c r="AV28" s="34"/>
       <c r="AW28" s="35"/>
-      <c r="AX28" s="36" t="str">
+      <c r="AX28" s="36">
         <f>IF(SUM(AU28:AW28)=0,"",ROUND(AVERAGE(AU28:AW28),0))</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="AY28" s="34">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AZ28" s="34"/>
       <c r="BA28" s="35"/>
       <c r="BB28" s="37">
         <f>IF(SUM(AY28:BA28)=0,"",ROUND(AVERAGE(AY28:BA28),0))</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BC28" s="38">
-        <v>51.0</v>
+        <v>57.0</v>
       </c>
       <c r="BD28" s="39"/>
       <c r="BE28" s="40"/>
       <c r="BF28" s="41">
         <f>IF(SUM(F28,J28,N28,R28,V28,Z28,AD28,AH28,AL28,AP28,AT28,AX28,BB28)=0,"",ROUND(AVERAGE(F28,J28,N28,R28,V28,Z28,AD28,AH28,AL28,AP28,AT28,AX28,BB28),2))</f>
-        <v>66.8</v>
+        <v>66.91</v>
       </c>
       <c r="BG28" s="31">
         <v>21</v>
       </c>
       <c r="BH28" s="32" t="str">
         <f>IF(B28="","",B28)</f>
-        <v>VASQUEZ GARCIA KAREN</v>
+        <v>VARGAS MENDIETA FABRICIO</v>
       </c>
       <c r="BI28" s="44">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="BJ28" s="42"/>
       <c r="BK28" s="43"/>
       <c r="BL28" s="45">
         <f>IF(SUM(BI28:BK28)=0,"",ROUND(AVERAGE(BI28:BK28),0))</f>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="BM28" s="44">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="BN28" s="42"/>
       <c r="BO28" s="43"/>
-      <c r="BP28" s="45" t="str">
+      <c r="BP28" s="45">
         <f>IF(SUM(BM28:BO28)=0,"",ROUND(AVERAGE(BM28:BO28),0))</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="BQ28" s="33">
-        <v>39.0</v>
+        <v>60.0</v>
       </c>
       <c r="BR28" s="34"/>
       <c r="BS28" s="35"/>
       <c r="BT28" s="36">
         <f>IF(SUM(BQ28:BS28)=0,"",ROUND(AVERAGE(BQ28:BS28),0))</f>
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -5811,17 +5856,17 @@
         <v>51</v>
       </c>
       <c r="C29" s="33">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D29" s="34"/>
       <c r="E29" s="35"/>
-      <c r="F29" s="36">
+      <c r="F29" s="36" t="str">
         <f>IF(SUM(C29:E29)=0,"",ROUND(AVERAGE(C29:E29),0))</f>
-        <v>41</v>
+        <v/>
       </c>
       <c r="G29" s="34">
         <f>IF(BQ29="","",BQ29)</f>
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="H29" s="34" t="str">
         <f>IF(BR29="","",BR29)</f>
@@ -5833,52 +5878,52 @@
       </c>
       <c r="J29" s="37">
         <f>IF(BT29="","",BT29)</f>
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="K29" s="33">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="35"/>
-      <c r="N29" s="36" t="str">
+      <c r="N29" s="36">
         <f>IF(SUM(K29:M29)=0,"",ROUND(AVERAGE(K29:M29),0))</f>
-        <v/>
+        <v>87</v>
       </c>
       <c r="O29" s="34">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="P29" s="34"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="37">
         <f>IF(SUM(O29:Q29)=0,"",ROUND(AVERAGE(O29:Q29),0))</f>
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="S29" s="33">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="T29" s="34"/>
       <c r="U29" s="35"/>
       <c r="V29" s="36">
         <f>IF(SUM(S29:U29)=0,"",ROUND(AVERAGE(S29:U29),0))</f>
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="W29" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="X29" s="34"/>
       <c r="Y29" s="35"/>
       <c r="Z29" s="36">
         <f>IF(SUM(W29:Y29)=0,"",ROUND(AVERAGE(W29:Y29),0))</f>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AA29" s="34">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="AB29" s="34"/>
       <c r="AC29" s="35"/>
       <c r="AD29" s="37">
         <f>IF(SUM(AA29:AC29)=0,"",ROUND(AVERAGE(AA29:AC29),0))</f>
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="AE29" s="33"/>
       <c r="AF29" s="34"/>
@@ -5888,90 +5933,92 @@
         <v/>
       </c>
       <c r="AI29" s="33">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="AJ29" s="34"/>
       <c r="AK29" s="35"/>
       <c r="AL29" s="36">
         <f>IF(SUM(AI29:AK29)=0,"",ROUND(AVERAGE(AI29:AK29),0))</f>
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="AM29" s="33">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AN29" s="34"/>
       <c r="AO29" s="35"/>
       <c r="AP29" s="36">
         <f>IF(SUM(AM29:AO29)=0,"",ROUND(AVERAGE(AM29:AO29),0))</f>
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AQ29" s="33">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="AR29" s="34"/>
       <c r="AS29" s="35"/>
       <c r="AT29" s="36">
         <f>IF(SUM(AQ29:AS29)=0,"",ROUND(AVERAGE(AQ29:AS29),0))</f>
-        <v>50</v>
-      </c>
-      <c r="AU29" s="33"/>
+        <v>89</v>
+      </c>
+      <c r="AU29" s="33">
+        <v>83</v>
+      </c>
       <c r="AV29" s="34"/>
       <c r="AW29" s="35"/>
-      <c r="AX29" s="36" t="str">
+      <c r="AX29" s="36">
         <f>IF(SUM(AU29:AW29)=0,"",ROUND(AVERAGE(AU29:AW29),0))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="AY29" s="34">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AZ29" s="34"/>
       <c r="BA29" s="35"/>
       <c r="BB29" s="37">
         <f>IF(SUM(AY29:BA29)=0,"",ROUND(AVERAGE(AY29:BA29),0))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BC29" s="38">
-        <v>51.0</v>
+        <v>78.0</v>
       </c>
       <c r="BD29" s="39"/>
       <c r="BE29" s="40"/>
       <c r="BF29" s="41">
         <f>IF(SUM(F29,J29,N29,R29,V29,Z29,AD29,AH29,AL29,AP29,AT29,AX29,BB29)=0,"",ROUND(AVERAGE(F29,J29,N29,R29,V29,Z29,AD29,AH29,AL29,AP29,AT29,AX29,BB29),2))</f>
-        <v>66.5</v>
+        <v>91.64</v>
       </c>
       <c r="BG29" s="31">
         <v>22</v>
       </c>
       <c r="BH29" s="32" t="str">
         <f>IF(B29="","",B29)</f>
-        <v>VEGA TERRAZAS LUCIANO GRECO</v>
+        <v>VASQUEZ GARCIA KAREN</v>
       </c>
       <c r="BI29" s="44">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="BJ29" s="42"/>
       <c r="BK29" s="43"/>
       <c r="BL29" s="45">
         <f>IF(SUM(BI29:BK29)=0,"",ROUND(AVERAGE(BI29:BK29),0))</f>
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="BM29" s="44">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BN29" s="42"/>
       <c r="BO29" s="43"/>
-      <c r="BP29" s="45" t="str">
+      <c r="BP29" s="45">
         <f>IF(SUM(BM29:BO29)=0,"",ROUND(AVERAGE(BM29:BO29),0))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="BQ29" s="33">
-        <v>34.0</v>
+        <v>92.0</v>
       </c>
       <c r="BR29" s="34"/>
       <c r="BS29" s="35"/>
       <c r="BT29" s="36">
         <f>IF(SUM(BQ29:BS29)=0,"",ROUND(AVERAGE(BQ29:BS29),0))</f>
-        <v>34</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -5982,17 +6029,17 @@
         <v>52</v>
       </c>
       <c r="C30" s="33">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="35"/>
-      <c r="F30" s="36">
+      <c r="F30" s="36" t="str">
         <f>IF(SUM(C30:E30)=0,"",ROUND(AVERAGE(C30:E30),0))</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="G30" s="34">
         <f>IF(BQ30="","",BQ30)</f>
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="H30" s="34" t="str">
         <f>IF(BR30="","",BR30)</f>
@@ -6004,52 +6051,52 @@
       </c>
       <c r="J30" s="37">
         <f>IF(BT30="","",BT30)</f>
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="K30" s="33">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="35"/>
-      <c r="N30" s="36" t="str">
+      <c r="N30" s="36">
         <f>IF(SUM(K30:M30)=0,"",ROUND(AVERAGE(K30:M30),0))</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="O30" s="34">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="P30" s="34"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="37">
         <f>IF(SUM(O30:Q30)=0,"",ROUND(AVERAGE(O30:Q30),0))</f>
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="S30" s="33">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="T30" s="34"/>
       <c r="U30" s="35"/>
       <c r="V30" s="36">
         <f>IF(SUM(S30:U30)=0,"",ROUND(AVERAGE(S30:U30),0))</f>
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="W30" s="33">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="X30" s="34"/>
       <c r="Y30" s="35"/>
       <c r="Z30" s="36">
         <f>IF(SUM(W30:Y30)=0,"",ROUND(AVERAGE(W30:Y30),0))</f>
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="AA30" s="34">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="AB30" s="34"/>
       <c r="AC30" s="35"/>
       <c r="AD30" s="37">
         <f>IF(SUM(AA30:AC30)=0,"",ROUND(AVERAGE(AA30:AC30),0))</f>
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="AE30" s="33"/>
       <c r="AF30" s="34"/>
@@ -6059,90 +6106,92 @@
         <v/>
       </c>
       <c r="AI30" s="33">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AJ30" s="34"/>
       <c r="AK30" s="35"/>
       <c r="AL30" s="36">
         <f>IF(SUM(AI30:AK30)=0,"",ROUND(AVERAGE(AI30:AK30),0))</f>
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AM30" s="33">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="AN30" s="34"/>
       <c r="AO30" s="35"/>
       <c r="AP30" s="36">
         <f>IF(SUM(AM30:AO30)=0,"",ROUND(AVERAGE(AM30:AO30),0))</f>
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="AQ30" s="33">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AR30" s="34"/>
       <c r="AS30" s="35"/>
       <c r="AT30" s="36">
         <f>IF(SUM(AQ30:AS30)=0,"",ROUND(AVERAGE(AQ30:AS30),0))</f>
-        <v>85</v>
-      </c>
-      <c r="AU30" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="AU30" s="33">
+        <v>93</v>
+      </c>
       <c r="AV30" s="34"/>
       <c r="AW30" s="35"/>
-      <c r="AX30" s="36" t="str">
+      <c r="AX30" s="36">
         <f>IF(SUM(AU30:AW30)=0,"",ROUND(AVERAGE(AU30:AW30),0))</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="AY30" s="34">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AZ30" s="34"/>
       <c r="BA30" s="35"/>
       <c r="BB30" s="37">
         <f>IF(SUM(AY30:BA30)=0,"",ROUND(AVERAGE(AY30:BA30),0))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BC30" s="38">
-        <v>26.0</v>
+        <v>74.0</v>
       </c>
       <c r="BD30" s="39"/>
       <c r="BE30" s="40"/>
       <c r="BF30" s="41">
         <f>IF(SUM(F30,J30,N30,R30,V30,Z30,AD30,AH30,AL30,AP30,AT30,AX30,BB30)=0,"",ROUND(AVERAGE(F30,J30,N30,R30,V30,Z30,AD30,AH30,AL30,AP30,AT30,AX30,BB30),2))</f>
-        <v>34.4</v>
+        <v>87.09</v>
       </c>
       <c r="BG30" s="31">
         <v>23</v>
       </c>
       <c r="BH30" s="32" t="str">
         <f>IF(B30="","",B30)</f>
-        <v>ZAMBRANA ALEJO MATEO</v>
+        <v>VEGA TERRAZAS LUCIANO GRECO</v>
       </c>
       <c r="BI30" s="44">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="BJ30" s="42"/>
       <c r="BK30" s="43"/>
       <c r="BL30" s="45">
         <f>IF(SUM(BI30:BK30)=0,"",ROUND(AVERAGE(BI30:BK30),0))</f>
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="BM30" s="44">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BN30" s="42"/>
       <c r="BO30" s="43"/>
-      <c r="BP30" s="45" t="str">
+      <c r="BP30" s="45">
         <f>IF(SUM(BM30:BO30)=0,"",ROUND(AVERAGE(BM30:BO30),0))</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="BQ30" s="33">
-        <v>21.0</v>
+        <v>79.0</v>
       </c>
       <c r="BR30" s="34"/>
       <c r="BS30" s="35"/>
       <c r="BT30" s="36">
         <f>IF(SUM(BQ30:BS30)=0,"",ROUND(AVERAGE(BQ30:BS30),0))</f>
-        <v>21</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -6153,17 +6202,17 @@
         <v>53</v>
       </c>
       <c r="C31" s="33">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="35"/>
-      <c r="F31" s="36">
+      <c r="F31" s="36" t="str">
         <f>IF(SUM(C31:E31)=0,"",ROUND(AVERAGE(C31:E31),0))</f>
-        <v>72</v>
+        <v/>
       </c>
       <c r="G31" s="34">
         <f>IF(BQ31="","",BQ31)</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H31" s="34" t="str">
         <f>IF(BR31="","",BR31)</f>
@@ -6175,16 +6224,16 @@
       </c>
       <c r="J31" s="37">
         <f>IF(BT31="","",BT31)</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K31" s="33">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35"/>
-      <c r="N31" s="36" t="str">
+      <c r="N31" s="36">
         <f>IF(SUM(K31:M31)=0,"",ROUND(AVERAGE(K31:M31),0))</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="O31" s="34">
         <v>81</v>
@@ -6196,31 +6245,31 @@
         <v>81</v>
       </c>
       <c r="S31" s="33">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="T31" s="34"/>
       <c r="U31" s="35"/>
       <c r="V31" s="36">
         <f>IF(SUM(S31:U31)=0,"",ROUND(AVERAGE(S31:U31),0))</f>
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="W31" s="33">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="X31" s="34"/>
       <c r="Y31" s="35"/>
       <c r="Z31" s="36">
         <f>IF(SUM(W31:Y31)=0,"",ROUND(AVERAGE(W31:Y31),0))</f>
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA31" s="34">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AB31" s="34"/>
       <c r="AC31" s="35"/>
       <c r="AD31" s="37">
         <f>IF(SUM(AA31:AC31)=0,"",ROUND(AVERAGE(AA31:AC31),0))</f>
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AE31" s="33"/>
       <c r="AF31" s="34"/>
@@ -6230,107 +6279,113 @@
         <v/>
       </c>
       <c r="AI31" s="33">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="35"/>
       <c r="AL31" s="36">
         <f>IF(SUM(AI31:AK31)=0,"",ROUND(AVERAGE(AI31:AK31),0))</f>
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="AM31" s="33">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="AN31" s="34"/>
       <c r="AO31" s="35"/>
       <c r="AP31" s="36">
         <f>IF(SUM(AM31:AO31)=0,"",ROUND(AVERAGE(AM31:AO31),0))</f>
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="AQ31" s="33">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="AR31" s="34"/>
       <c r="AS31" s="35"/>
       <c r="AT31" s="36">
         <f>IF(SUM(AQ31:AS31)=0,"",ROUND(AVERAGE(AQ31:AS31),0))</f>
-        <v>72</v>
-      </c>
-      <c r="AU31" s="33"/>
+        <v>45</v>
+      </c>
+      <c r="AU31" s="33">
+        <v>51</v>
+      </c>
       <c r="AV31" s="34"/>
       <c r="AW31" s="35"/>
-      <c r="AX31" s="36" t="str">
+      <c r="AX31" s="36">
         <f>IF(SUM(AU31:AW31)=0,"",ROUND(AVERAGE(AU31:AW31),0))</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="AY31" s="34">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AZ31" s="34"/>
       <c r="BA31" s="35"/>
       <c r="BB31" s="37">
         <f>IF(SUM(AY31:BA31)=0,"",ROUND(AVERAGE(AY31:BA31),0))</f>
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="BC31" s="38">
-        <v>54.0</v>
+        <v>43.0</v>
       </c>
       <c r="BD31" s="39"/>
       <c r="BE31" s="40"/>
       <c r="BF31" s="41">
         <f>IF(SUM(F31,J31,N31,R31,V31,Z31,AD31,AH31,AL31,AP31,AT31,AX31,BB31)=0,"",ROUND(AVERAGE(F31,J31,N31,R31,V31,Z31,AD31,AH31,AL31,AP31,AT31,AX31,BB31),2))</f>
-        <v>69.8</v>
+        <v>50.73</v>
       </c>
       <c r="BG31" s="31">
         <v>24</v>
       </c>
       <c r="BH31" s="32" t="str">
         <f>IF(B31="","",B31)</f>
-        <v>ZAMBRANA HERBAS MARIA BELEN</v>
+        <v>ZAMBRANA ALEJO MATEO</v>
       </c>
       <c r="BI31" s="44">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="BJ31" s="42"/>
       <c r="BK31" s="43"/>
       <c r="BL31" s="45">
         <f>IF(SUM(BI31:BK31)=0,"",ROUND(AVERAGE(BI31:BK31),0))</f>
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="BM31" s="44">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="BN31" s="42"/>
       <c r="BO31" s="43"/>
-      <c r="BP31" s="45" t="str">
+      <c r="BP31" s="45">
         <f>IF(SUM(BM31:BO31)=0,"",ROUND(AVERAGE(BM31:BO31),0))</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="BQ31" s="33">
-        <v>39.0</v>
+        <v>37.0</v>
       </c>
       <c r="BR31" s="34"/>
       <c r="BS31" s="35"/>
       <c r="BT31" s="36">
         <f>IF(SUM(BQ31:BS31)=0,"",ROUND(AVERAGE(BQ31:BS31),0))</f>
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" s="31">
         <v>25</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
+      <c r="B32" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="33">
+        <v>0</v>
+      </c>
       <c r="D32" s="34"/>
       <c r="E32" s="35"/>
       <c r="F32" s="36" t="str">
         <f>IF(SUM(C32:E32)=0,"",ROUND(AVERAGE(C32:E32),0))</f>
         <v/>
       </c>
-      <c r="G32" s="34" t="str">
+      <c r="G32" s="34">
         <f>IF(BQ32="","",BQ32)</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H32" s="34" t="str">
         <f>IF(BR32="","",BR32)</f>
@@ -6340,44 +6395,54 @@
         <f>IF(BS32="","",BS32)</f>
         <v/>
       </c>
-      <c r="J32" s="37" t="str">
+      <c r="J32" s="37">
         <f>IF(BT32="","",BT32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="33"/>
+        <v>90</v>
+      </c>
+      <c r="K32" s="33">
+        <v>85</v>
+      </c>
       <c r="L32" s="34"/>
       <c r="M32" s="35"/>
-      <c r="N32" s="36" t="str">
+      <c r="N32" s="36">
         <f>IF(SUM(K32:M32)=0,"",ROUND(AVERAGE(K32:M32),0))</f>
-        <v/>
-      </c>
-      <c r="O32" s="34"/>
+        <v>85</v>
+      </c>
+      <c r="O32" s="34">
+        <v>94</v>
+      </c>
       <c r="P32" s="34"/>
       <c r="Q32" s="35"/>
-      <c r="R32" s="37" t="str">
+      <c r="R32" s="37">
         <f>IF(SUM(O32:Q32)=0,"",ROUND(AVERAGE(O32:Q32),0))</f>
-        <v/>
-      </c>
-      <c r="S32" s="33"/>
+        <v>94</v>
+      </c>
+      <c r="S32" s="33">
+        <v>99</v>
+      </c>
       <c r="T32" s="34"/>
       <c r="U32" s="35"/>
-      <c r="V32" s="36" t="str">
+      <c r="V32" s="36">
         <f>IF(SUM(S32:U32)=0,"",ROUND(AVERAGE(S32:U32),0))</f>
-        <v/>
-      </c>
-      <c r="W32" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="W32" s="33">
+        <v>98</v>
+      </c>
       <c r="X32" s="34"/>
       <c r="Y32" s="35"/>
-      <c r="Z32" s="36" t="str">
+      <c r="Z32" s="36">
         <f>IF(SUM(W32:Y32)=0,"",ROUND(AVERAGE(W32:Y32),0))</f>
-        <v/>
-      </c>
-      <c r="AA32" s="34"/>
+        <v>98</v>
+      </c>
+      <c r="AA32" s="34">
+        <v>95</v>
+      </c>
       <c r="AB32" s="34"/>
       <c r="AC32" s="35"/>
-      <c r="AD32" s="37" t="str">
+      <c r="AD32" s="37">
         <f>IF(SUM(AA32:AC32)=0,"",ROUND(AVERAGE(AA32:AC32),0))</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="AE32" s="33"/>
       <c r="AF32" s="34"/>
@@ -6386,75 +6451,93 @@
         <f>IF(SUM(AE32:AG32)=0,"",ROUND(AVERAGE(AE32:AG32),0))</f>
         <v/>
       </c>
-      <c r="AI32" s="33"/>
+      <c r="AI32" s="33">
+        <v>91</v>
+      </c>
       <c r="AJ32" s="34"/>
       <c r="AK32" s="35"/>
-      <c r="AL32" s="36" t="str">
+      <c r="AL32" s="36">
         <f>IF(SUM(AI32:AK32)=0,"",ROUND(AVERAGE(AI32:AK32),0))</f>
-        <v/>
-      </c>
-      <c r="AM32" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="AM32" s="33">
+        <v>100</v>
+      </c>
       <c r="AN32" s="34"/>
       <c r="AO32" s="35"/>
-      <c r="AP32" s="36" t="str">
+      <c r="AP32" s="36">
         <f>IF(SUM(AM32:AO32)=0,"",ROUND(AVERAGE(AM32:AO32),0))</f>
-        <v/>
-      </c>
-      <c r="AQ32" s="33"/>
+        <v>100</v>
+      </c>
+      <c r="AQ32" s="33">
+        <v>95</v>
+      </c>
       <c r="AR32" s="34"/>
       <c r="AS32" s="35"/>
-      <c r="AT32" s="36" t="str">
+      <c r="AT32" s="36">
         <f>IF(SUM(AQ32:AS32)=0,"",ROUND(AVERAGE(AQ32:AS32),0))</f>
-        <v/>
-      </c>
-      <c r="AU32" s="33"/>
+        <v>95</v>
+      </c>
+      <c r="AU32" s="33">
+        <v>99</v>
+      </c>
       <c r="AV32" s="34"/>
       <c r="AW32" s="35"/>
-      <c r="AX32" s="36" t="str">
+      <c r="AX32" s="36">
         <f>IF(SUM(AU32:AW32)=0,"",ROUND(AVERAGE(AU32:AW32),0))</f>
-        <v/>
-      </c>
-      <c r="AY32" s="34"/>
+        <v>99</v>
+      </c>
+      <c r="AY32" s="34">
+        <v>98</v>
+      </c>
       <c r="AZ32" s="34"/>
       <c r="BA32" s="35"/>
-      <c r="BB32" s="37" t="str">
+      <c r="BB32" s="37">
         <f>IF(SUM(AY32:BA32)=0,"",ROUND(AVERAGE(AY32:BA32),0))</f>
-        <v/>
-      </c>
-      <c r="BC32" s="38"/>
+        <v>98</v>
+      </c>
+      <c r="BC32" s="38">
+        <v>80.0</v>
+      </c>
       <c r="BD32" s="39"/>
       <c r="BE32" s="40"/>
-      <c r="BF32" s="41" t="str">
+      <c r="BF32" s="41">
         <f>IF(SUM(F32,J32,N32,R32,V32,Z32,AD32,AH32,AL32,AP32,AT32,AX32,BB32)=0,"",ROUND(AVERAGE(F32,J32,N32,R32,V32,Z32,AD32,AH32,AL32,AP32,AT32,AX32,BB32),2))</f>
-        <v/>
+        <v>94.91</v>
       </c>
       <c r="BG32" s="31">
         <v>25</v>
       </c>
       <c r="BH32" s="32" t="str">
         <f>IF(B32="","",B32)</f>
-        <v/>
-      </c>
-      <c r="BI32" s="44"/>
+        <v>ZAMBRANA HERBAS MARIA BELEN</v>
+      </c>
+      <c r="BI32" s="44">
+        <v>92</v>
+      </c>
       <c r="BJ32" s="42"/>
       <c r="BK32" s="43"/>
-      <c r="BL32" s="45" t="str">
+      <c r="BL32" s="45">
         <f>IF(SUM(BI32:BK32)=0,"",ROUND(AVERAGE(BI32:BK32),0))</f>
-        <v/>
-      </c>
-      <c r="BM32" s="44"/>
+        <v>92</v>
+      </c>
+      <c r="BM32" s="44">
+        <v>88</v>
+      </c>
       <c r="BN32" s="42"/>
       <c r="BO32" s="43"/>
-      <c r="BP32" s="45" t="str">
+      <c r="BP32" s="45">
         <f>IF(SUM(BM32:BO32)=0,"",ROUND(AVERAGE(BM32:BO32),0))</f>
-        <v/>
-      </c>
-      <c r="BQ32" s="33"/>
+        <v>88</v>
+      </c>
+      <c r="BQ32" s="33">
+        <v>90.0</v>
+      </c>
       <c r="BR32" s="34"/>
       <c r="BS32" s="35"/>
-      <c r="BT32" s="36" t="str">
+      <c r="BT32" s="36">
         <f>IF(SUM(BQ32:BS32)=0,"",ROUND(AVERAGE(BQ32:BS32),0))</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -7164,12 +7247,12 @@
     </row>
     <row r="38" spans="1:80">
       <c r="A38" s="106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38" s="107"/>
       <c r="C38" s="62">
         <f>IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
-        <v>44.083333333333</v>
+        <v>10.92</v>
       </c>
       <c r="D38" s="63" t="str">
         <f>IF(SUM(D8:D37)=0,"",AVERAGE(D8:D37))</f>
@@ -7181,11 +7264,11 @@
       </c>
       <c r="F38" s="65">
         <f>IF(SUM(F8:F37)=0,"",AVERAGE(F8:F37))</f>
-        <v>44.083333333333</v>
+        <v>68.25</v>
       </c>
       <c r="G38" s="62">
         <f>IF(SUM(G8:G37)=0,"",AVERAGE(G8:G37))</f>
-        <v>30.5</v>
+        <v>73.32</v>
       </c>
       <c r="H38" s="63" t="str">
         <f>IF(SUM(H8:H37)=0,"",AVERAGE(H8:H37))</f>
@@ -7197,11 +7280,11 @@
       </c>
       <c r="J38" s="65">
         <f>IF(SUM(J8:J37)=0,"",AVERAGE(J8:J37))</f>
-        <v>30.5</v>
-      </c>
-      <c r="K38" s="62" t="str">
+        <v>73.32</v>
+      </c>
+      <c r="K38" s="62">
         <f>IF(SUM(K8:K37)=0,"",AVERAGE(K8:K37))</f>
-        <v/>
+        <v>68.68</v>
       </c>
       <c r="L38" s="63" t="str">
         <f>IF(SUM(L8:L37)=0,"",AVERAGE(L8:L37))</f>
@@ -7211,13 +7294,13 @@
         <f>IF(SUM(M8:M37)=0,"",AVERAGE(M8:M37))</f>
         <v/>
       </c>
-      <c r="N38" s="65" t="str">
+      <c r="N38" s="65">
         <f>IF(SUM(N8:N37)=0,"",AVERAGE(N8:N37))</f>
-        <v/>
+        <v>68.68</v>
       </c>
       <c r="O38" s="63">
         <f>IF(SUM(O8:O37)=0,"",AVERAGE(O8:O37))</f>
-        <v>75.333333333333</v>
+        <v>91.76</v>
       </c>
       <c r="P38" s="63" t="str">
         <f>IF(SUM(P8:P37)=0,"",AVERAGE(P8:P37))</f>
@@ -7229,11 +7312,11 @@
       </c>
       <c r="R38" s="66">
         <f>IF(SUM(R8:R37)=0,"",AVERAGE(R8:R37))</f>
-        <v>75.333333333333</v>
+        <v>91.76</v>
       </c>
       <c r="S38" s="62">
         <f>IF(SUM(S8:S37)=0,"",AVERAGE(S8:S37))</f>
-        <v>64.666666666667</v>
+        <v>87.68</v>
       </c>
       <c r="T38" s="63" t="str">
         <f>IF(SUM(T8:T37)=0,"",AVERAGE(T8:T37))</f>
@@ -7245,11 +7328,11 @@
       </c>
       <c r="V38" s="65">
         <f>IF(SUM(V8:V37)=0,"",AVERAGE(V8:V37))</f>
-        <v>64.666666666667</v>
+        <v>87.68</v>
       </c>
       <c r="W38" s="62">
         <f>IF(SUM(W8:W37)=0,"",AVERAGE(W8:W37))</f>
-        <v>47.333333333333</v>
+        <v>77.32</v>
       </c>
       <c r="X38" s="63" t="str">
         <f>IF(SUM(X8:X37)=0,"",AVERAGE(X8:X37))</f>
@@ -7261,11 +7344,11 @@
       </c>
       <c r="Z38" s="65">
         <f>IF(SUM(Z8:Z37)=0,"",AVERAGE(Z8:Z37))</f>
-        <v>47.333333333333</v>
+        <v>77.32</v>
       </c>
       <c r="AA38" s="63">
         <f>IF(SUM(AA8:AA37)=0,"",AVERAGE(AA8:AA37))</f>
-        <v>58.625</v>
+        <v>70.48</v>
       </c>
       <c r="AB38" s="63" t="str">
         <f>IF(SUM(AB8:AB37)=0,"",AVERAGE(AB8:AB37))</f>
@@ -7277,7 +7360,7 @@
       </c>
       <c r="AD38" s="66">
         <f>IF(SUM(AD8:AD37)=0,"",AVERAGE(AD8:AD37))</f>
-        <v>58.625</v>
+        <v>70.48</v>
       </c>
       <c r="AE38" s="62" t="str">
         <f>IF(SUM(AE8:AE37)=0,"",AVERAGE(AE8:AE37))</f>
@@ -7297,7 +7380,7 @@
       </c>
       <c r="AI38" s="62">
         <f>IF(SUM(AI8:AI37)=0,"",AVERAGE(AI8:AI37))</f>
-        <v>56.625</v>
+        <v>72.64</v>
       </c>
       <c r="AJ38" s="63" t="str">
         <f>IF(SUM(AJ8:AJ37)=0,"",AVERAGE(AJ8:AJ37))</f>
@@ -7309,11 +7392,11 @@
       </c>
       <c r="AL38" s="65">
         <f>IF(SUM(AL8:AL37)=0,"",AVERAGE(AL8:AL37))</f>
-        <v>56.625</v>
+        <v>72.64</v>
       </c>
       <c r="AM38" s="62">
         <f>IF(SUM(AM8:AM37)=0,"",AVERAGE(AM8:AM37))</f>
-        <v>48.875</v>
+        <v>71.6</v>
       </c>
       <c r="AN38" s="63" t="str">
         <f>IF(SUM(AN8:AN37)=0,"",AVERAGE(AN8:AN37))</f>
@@ -7325,11 +7408,11 @@
       </c>
       <c r="AP38" s="65">
         <f>IF(SUM(AP8:AP37)=0,"",AVERAGE(AP8:AP37))</f>
-        <v>48.875</v>
+        <v>71.6</v>
       </c>
       <c r="AQ38" s="62">
         <f>IF(SUM(AQ8:AQ37)=0,"",AVERAGE(AQ8:AQ37))</f>
-        <v>59.125</v>
+        <v>70.08</v>
       </c>
       <c r="AR38" s="63" t="str">
         <f>IF(SUM(AR8:AR37)=0,"",AVERAGE(AR8:AR37))</f>
@@ -7341,11 +7424,11 @@
       </c>
       <c r="AT38" s="65">
         <f>IF(SUM(AT8:AT37)=0,"",AVERAGE(AT8:AT37))</f>
-        <v>59.125</v>
-      </c>
-      <c r="AU38" s="62" t="str">
+        <v>70.08</v>
+      </c>
+      <c r="AU38" s="62">
         <f>IF(SUM(AU8:AU37)=0,"",AVERAGE(AU8:AU37))</f>
-        <v/>
+        <v>69.08</v>
       </c>
       <c r="AV38" s="63" t="str">
         <f>IF(SUM(AV8:AV37)=0,"",AVERAGE(AV8:AV37))</f>
@@ -7355,13 +7438,13 @@
         <f>IF(SUM(AW8:AW37)=0,"",AVERAGE(AW8:AW37))</f>
         <v/>
       </c>
-      <c r="AX38" s="65" t="str">
+      <c r="AX38" s="65">
         <f>IF(SUM(AX8:AX37)=0,"",AVERAGE(AX8:AX37))</f>
-        <v/>
+        <v>69.08</v>
       </c>
       <c r="AY38" s="63">
         <f>IF(SUM(AY8:AY37)=0,"",AVERAGE(AY8:AY37))</f>
-        <v>65.125</v>
+        <v>89.84</v>
       </c>
       <c r="AZ38" s="63" t="str">
         <f>IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
@@ -7373,11 +7456,11 @@
       </c>
       <c r="BB38" s="66">
         <f>IF(SUM(BB8:BB37)=0,"",AVERAGE(BB8:BB37))</f>
-        <v>65.125</v>
+        <v>89.84</v>
       </c>
       <c r="BC38" s="67">
         <f>IF(SUM(BC8:BC37)=0,"",AVERAGE(BC8:BC37))</f>
-        <v>42.25</v>
+        <v>65.64</v>
       </c>
       <c r="BD38" s="68" t="str">
         <f>IF(SUM(BD8:BD37)=0,"",AVERAGE(BD8:BD37))</f>
@@ -7389,15 +7472,15 @@
       </c>
       <c r="BF38" s="70">
         <f>IF(SUM(BF8:BF37)=0,"",AVERAGE(BF8:BF37))</f>
-        <v>55.029166666667</v>
+        <v>76.508</v>
       </c>
       <c r="BG38" s="106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BH38" s="107"/>
       <c r="BI38" s="73">
         <f>IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
-        <v>60.458333333333</v>
+        <v>75.08</v>
       </c>
       <c r="BJ38" s="71" t="str">
         <f>IF(SUM(BJ8:BJ37)=0,"",AVERAGE(BJ8:BJ37))</f>
@@ -7409,11 +7492,11 @@
       </c>
       <c r="BL38" s="74">
         <f>IF(SUM(BL8:BL37)=0,"",AVERAGE(BL8:BL37))</f>
-        <v>60.458333333333</v>
-      </c>
-      <c r="BM38" s="73" t="str">
+        <v>75.08</v>
+      </c>
+      <c r="BM38" s="73">
         <f>IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
-        <v/>
+        <v>70.84</v>
       </c>
       <c r="BN38" s="71" t="str">
         <f>IF(SUM(BN8:BN37)=0,"",AVERAGE(BN8:BN37))</f>
@@ -7423,13 +7506,13 @@
         <f>IF(SUM(BO8:BO37)=0,"",AVERAGE(BO8:BO37))</f>
         <v/>
       </c>
-      <c r="BP38" s="74" t="str">
+      <c r="BP38" s="74">
         <f>IF(SUM(BP8:BP37)=0,"",AVERAGE(BP8:BP37))</f>
-        <v/>
+        <v>70.84</v>
       </c>
       <c r="BQ38" s="62">
         <f>IF(SUM(BQ8:BQ37)=0,"",AVERAGE(BQ8:BQ37))</f>
-        <v>30.5</v>
+        <v>73.32</v>
       </c>
       <c r="BR38" s="63" t="str">
         <f>IF(SUM(BR8:BR37)=0,"",AVERAGE(BR8:BR37))</f>
@@ -7441,17 +7524,17 @@
       </c>
       <c r="BT38" s="65">
         <f>IF(SUM(BT8:BT37)=0,"",AVERAGE(BT8:BT37))</f>
-        <v>30.5</v>
+        <v>73.32</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" s="92" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B39" s="93"/>
       <c r="C39" s="62">
         <f>IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="D39" s="63" t="str">
         <f>IF(SUM(D8:D37)=0,"",MEDIAN(D8:D37))</f>
@@ -7463,11 +7546,11 @@
       </c>
       <c r="F39" s="65">
         <f>IF(SUM(F8:F37)=0,"",MEDIAN(F8:F37))</f>
-        <v>50.5</v>
+        <v>66</v>
       </c>
       <c r="G39" s="62">
         <f>IF(SUM(G8:G37)=0,"",MEDIAN(G8:G37))</f>
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="H39" s="63" t="str">
         <f>IF(SUM(H8:H37)=0,"",MEDIAN(H8:H37))</f>
@@ -7479,11 +7562,11 @@
       </c>
       <c r="J39" s="65">
         <f>IF(SUM(J8:J37)=0,"",MEDIAN(J8:J37))</f>
-        <v>34</v>
-      </c>
-      <c r="K39" s="62" t="str">
+        <v>77</v>
+      </c>
+      <c r="K39" s="62">
         <f>IF(SUM(K8:K37)=0,"",MEDIAN(K8:K37))</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="L39" s="63" t="str">
         <f>IF(SUM(L8:L37)=0,"",MEDIAN(L8:L37))</f>
@@ -7493,13 +7576,13 @@
         <f>IF(SUM(M8:M37)=0,"",MEDIAN(M8:M37))</f>
         <v/>
       </c>
-      <c r="N39" s="65" t="str">
+      <c r="N39" s="65">
         <f>IF(SUM(N8:N37)=0,"",MEDIAN(N8:N37))</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="O39" s="63">
         <f>IF(SUM(O8:O37)=0,"",MEDIAN(O8:O37))</f>
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="P39" s="63" t="str">
         <f>IF(SUM(P8:P37)=0,"",MEDIAN(P8:P37))</f>
@@ -7511,11 +7594,11 @@
       </c>
       <c r="R39" s="66">
         <f>IF(SUM(R8:R37)=0,"",MEDIAN(R8:R37))</f>
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="S39" s="62">
         <f>IF(SUM(S8:S37)=0,"",MEDIAN(S8:S37))</f>
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="T39" s="63" t="str">
         <f>IF(SUM(T8:T37)=0,"",MEDIAN(T8:T37))</f>
@@ -7527,11 +7610,11 @@
       </c>
       <c r="V39" s="65">
         <f>IF(SUM(V8:V37)=0,"",MEDIAN(V8:V37))</f>
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="W39" s="62">
         <f>IF(SUM(W8:W37)=0,"",MEDIAN(W8:W37))</f>
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="X39" s="63" t="str">
         <f>IF(SUM(X8:X37)=0,"",MEDIAN(X8:X37))</f>
@@ -7543,11 +7626,11 @@
       </c>
       <c r="Z39" s="65">
         <f>IF(SUM(Z8:Z37)=0,"",MEDIAN(Z8:Z37))</f>
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="AA39" s="63">
         <f>IF(SUM(AA8:AA37)=0,"",MEDIAN(AA8:AA37))</f>
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="AB39" s="63" t="str">
         <f>IF(SUM(AB8:AB37)=0,"",MEDIAN(AB8:AB37))</f>
@@ -7559,7 +7642,7 @@
       </c>
       <c r="AD39" s="66">
         <f>IF(SUM(AD8:AD37)=0,"",MEDIAN(AD8:AD37))</f>
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="AE39" s="62" t="str">
         <f>IF(SUM(AE8:AE37)=0,"",MEDIAN(AE8:AE37))</f>
@@ -7579,7 +7662,7 @@
       </c>
       <c r="AI39" s="62">
         <f>IF(SUM(AI8:AI37)=0,"",MEDIAN(AI8:AI37))</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ39" s="63" t="str">
         <f>IF(SUM(AJ8:AJ37)=0,"",MEDIAN(AJ8:AJ37))</f>
@@ -7591,11 +7674,11 @@
       </c>
       <c r="AL39" s="65">
         <f>IF(SUM(AL8:AL37)=0,"",MEDIAN(AL8:AL37))</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM39" s="62">
         <f>IF(SUM(AM8:AM37)=0,"",MEDIAN(AM8:AM37))</f>
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="AN39" s="63" t="str">
         <f>IF(SUM(AN8:AN37)=0,"",MEDIAN(AN8:AN37))</f>
@@ -7607,11 +7690,11 @@
       </c>
       <c r="AP39" s="65">
         <f>IF(SUM(AP8:AP37)=0,"",MEDIAN(AP8:AP37))</f>
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="AQ39" s="62">
         <f>IF(SUM(AQ8:AQ37)=0,"",MEDIAN(AQ8:AQ37))</f>
-        <v>66.5</v>
+        <v>70</v>
       </c>
       <c r="AR39" s="63" t="str">
         <f>IF(SUM(AR8:AR37)=0,"",MEDIAN(AR8:AR37))</f>
@@ -7623,11 +7706,11 @@
       </c>
       <c r="AT39" s="65">
         <f>IF(SUM(AT8:AT37)=0,"",MEDIAN(AT8:AT37))</f>
-        <v>66.5</v>
-      </c>
-      <c r="AU39" s="62" t="str">
+        <v>70</v>
+      </c>
+      <c r="AU39" s="62">
         <f>IF(SUM(AU8:AU37)=0,"",MEDIAN(AU8:AU37))</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="AV39" s="63" t="str">
         <f>IF(SUM(AV8:AV37)=0,"",MEDIAN(AV8:AV37))</f>
@@ -7637,13 +7720,13 @@
         <f>IF(SUM(AW8:AW37)=0,"",MEDIAN(AW8:AW37))</f>
         <v/>
       </c>
-      <c r="AX39" s="65" t="str">
+      <c r="AX39" s="65">
         <f>IF(SUM(AX8:AX37)=0,"",MEDIAN(AX8:AX37))</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="AY39" s="63">
         <f>IF(SUM(AY8:AY37)=0,"",MEDIAN(AY8:AY37))</f>
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AZ39" s="63" t="str">
         <f>IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
@@ -7655,11 +7738,11 @@
       </c>
       <c r="BB39" s="66">
         <f>IF(SUM(BB8:BB37)=0,"",MEDIAN(BB8:BB37))</f>
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="BC39" s="67">
         <f>IF(SUM(BC8:BC37)=0,"",MEDIAN(BC8:BC37))</f>
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="BD39" s="68" t="str">
         <f>IF(SUM(BD8:BD37)=0,"",MEDIAN(BD8:BD37))</f>
@@ -7671,15 +7754,15 @@
       </c>
       <c r="BF39" s="70">
         <f>IF(SUM(BF8:BF37)=0,"",MEDIAN(BF8:BF37))</f>
-        <v>58.3</v>
+        <v>81.27</v>
       </c>
       <c r="BG39" s="92" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BH39" s="93"/>
       <c r="BI39" s="73">
         <f>IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
-        <v>67.5</v>
+        <v>79</v>
       </c>
       <c r="BJ39" s="71" t="str">
         <f>IF(SUM(BJ8:BJ37)=0,"",MEDIAN(BJ8:BJ37))</f>
@@ -7691,11 +7774,11 @@
       </c>
       <c r="BL39" s="74">
         <f>IF(SUM(BL8:BL37)=0,"",MEDIAN(BL8:BL37))</f>
-        <v>67.5</v>
-      </c>
-      <c r="BM39" s="73" t="str">
+        <v>79</v>
+      </c>
+      <c r="BM39" s="73">
         <f>IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="BN39" s="71" t="str">
         <f>IF(SUM(BN8:BN37)=0,"",MEDIAN(BN8:BN37))</f>
@@ -7705,13 +7788,13 @@
         <f>IF(SUM(BO8:BO37)=0,"",MEDIAN(BO8:BO37))</f>
         <v/>
       </c>
-      <c r="BP39" s="74" t="str">
+      <c r="BP39" s="74">
         <f>IF(SUM(BP8:BP37)=0,"",MEDIAN(BP8:BP37))</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="BQ39" s="62">
         <f>IF(SUM(BQ8:BQ37)=0,"",MEDIAN(BQ8:BQ37))</f>
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="BR39" s="63" t="str">
         <f>IF(SUM(BR8:BR37)=0,"",MEDIAN(BR8:BR37))</f>
@@ -7723,17 +7806,17 @@
       </c>
       <c r="BT39" s="65">
         <f>IF(SUM(BT8:BT37)=0,"",MEDIAN(BT8:BT37))</f>
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" s="92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B40" s="93"/>
       <c r="C40" s="62">
         <f>IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D40" s="63" t="str">
         <f>IF(SUM(D8:D37)=0,"",MAX(D8:D37))</f>
@@ -7745,11 +7828,11 @@
       </c>
       <c r="F40" s="65">
         <f>IF(SUM(F8:F37)=0,"",MAX(F8:F37))</f>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G40" s="63">
         <f>IF(SUM(G8:G37)=0,"",MAX(G8:G37))</f>
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H40" s="63" t="str">
         <f>IF(SUM(H8:H37)=0,"",MAX(H8:H37))</f>
@@ -7761,11 +7844,11 @@
       </c>
       <c r="J40" s="66">
         <f>IF(SUM(J8:J37)=0,"",MAX(J8:J37))</f>
-        <v>39</v>
-      </c>
-      <c r="K40" s="62" t="str">
+        <v>92</v>
+      </c>
+      <c r="K40" s="62">
         <f>IF(SUM(K8:K37)=0,"",MAX(K8:K37))</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="L40" s="63" t="str">
         <f>IF(SUM(L8:L37)=0,"",MAX(L8:L37))</f>
@@ -7775,13 +7858,13 @@
         <f>IF(SUM(M8:M37)=0,"",MAX(M8:M37))</f>
         <v/>
       </c>
-      <c r="N40" s="65" t="str">
+      <c r="N40" s="65">
         <f>IF(SUM(N8:N37)=0,"",MAX(N8:N37))</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="O40" s="63">
         <f>IF(SUM(O8:O37)=0,"",MAX(O8:O37))</f>
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P40" s="63" t="str">
         <f>IF(SUM(P8:P37)=0,"",MAX(P8:P37))</f>
@@ -7793,11 +7876,11 @@
       </c>
       <c r="R40" s="66">
         <f>IF(SUM(R8:R37)=0,"",MAX(R8:R37))</f>
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="S40" s="62">
         <f>IF(SUM(S8:S37)=0,"",MAX(S8:S37))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T40" s="63" t="str">
         <f>IF(SUM(T8:T37)=0,"",MAX(T8:T37))</f>
@@ -7809,11 +7892,11 @@
       </c>
       <c r="V40" s="65">
         <f>IF(SUM(V8:V37)=0,"",MAX(V8:V37))</f>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="W40" s="62">
         <f>IF(SUM(W8:W37)=0,"",MAX(W8:W37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X40" s="63" t="str">
         <f>IF(SUM(X8:X37)=0,"",MAX(X8:X37))</f>
@@ -7825,11 +7908,11 @@
       </c>
       <c r="Z40" s="65">
         <f>IF(SUM(Z8:Z37)=0,"",MAX(Z8:Z37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AA40" s="63">
         <f>IF(SUM(AA8:AA37)=0,"",MAX(AA8:AA37))</f>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AB40" s="63" t="str">
         <f>IF(SUM(AB8:AB37)=0,"",MAX(AB8:AB37))</f>
@@ -7841,7 +7924,7 @@
       </c>
       <c r="AD40" s="66">
         <f>IF(SUM(AD8:AD37)=0,"",MAX(AD8:AD37))</f>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AE40" s="62" t="str">
         <f>IF(SUM(AE8:AE37)=0,"",MAX(AE8:AE37))</f>
@@ -7861,7 +7944,7 @@
       </c>
       <c r="AI40" s="62">
         <f>IF(SUM(AI8:AI37)=0,"",MAX(AI8:AI37))</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ40" s="63" t="str">
         <f>IF(SUM(AJ8:AJ37)=0,"",MAX(AJ8:AJ37))</f>
@@ -7873,11 +7956,11 @@
       </c>
       <c r="AL40" s="65">
         <f>IF(SUM(AL8:AL37)=0,"",MAX(AL8:AL37))</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM40" s="62">
         <f>IF(SUM(AM8:AM37)=0,"",MAX(AM8:AM37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN40" s="63" t="str">
         <f>IF(SUM(AN8:AN37)=0,"",MAX(AN8:AN37))</f>
@@ -7889,11 +7972,11 @@
       </c>
       <c r="AP40" s="65">
         <f>IF(SUM(AP8:AP37)=0,"",MAX(AP8:AP37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AQ40" s="62">
         <f>IF(SUM(AQ8:AQ37)=0,"",MAX(AQ8:AQ37))</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AR40" s="63" t="str">
         <f>IF(SUM(AR8:AR37)=0,"",MAX(AR8:AR37))</f>
@@ -7905,11 +7988,11 @@
       </c>
       <c r="AT40" s="65">
         <f>IF(SUM(AT8:AT37)=0,"",MAX(AT8:AT37))</f>
-        <v>85</v>
-      </c>
-      <c r="AU40" s="62" t="str">
+        <v>95</v>
+      </c>
+      <c r="AU40" s="62">
         <f>IF(SUM(AU8:AU37)=0,"",MAX(AU8:AU37))</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="AV40" s="63" t="str">
         <f>IF(SUM(AV8:AV37)=0,"",MAX(AV8:AV37))</f>
@@ -7919,13 +8002,13 @@
         <f>IF(SUM(AW8:AW37)=0,"",MAX(AW8:AW37))</f>
         <v/>
       </c>
-      <c r="AX40" s="65" t="str">
+      <c r="AX40" s="65">
         <f>IF(SUM(AX8:AX37)=0,"",MAX(AX8:AX37))</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="AY40" s="63">
         <f>IF(SUM(AY8:AY37)=0,"",MAX(AY8:AY37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AZ40" s="63" t="str">
         <f>IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
@@ -7937,11 +8020,11 @@
       </c>
       <c r="BB40" s="66">
         <f>IF(SUM(BB8:BB37)=0,"",MAX(BB8:BB37))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BC40" s="67">
         <f>IF(SUM(BC8:BC37)=0,"",MAX(BC8:BC37))</f>
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="BD40" s="68" t="str">
         <f>IF(SUM(BD8:BD37)=0,"",MAX(BD8:BD37))</f>
@@ -7953,15 +8036,15 @@
       </c>
       <c r="BF40" s="70">
         <f>IF(SUM(BF8:BF37)=0,"",MAX(BF8:BF37))</f>
-        <v>72.9</v>
+        <v>94.91</v>
       </c>
       <c r="BG40" s="92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BH40" s="93"/>
       <c r="BI40" s="73">
         <f>IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="BJ40" s="71" t="str">
         <f>IF(SUM(BJ8:BJ37)=0,"",MAX(BJ8:BJ37))</f>
@@ -7973,11 +8056,11 @@
       </c>
       <c r="BL40" s="74">
         <f>IF(SUM(BL8:BL37)=0,"",MAX(BL8:BL37))</f>
-        <v>78</v>
-      </c>
-      <c r="BM40" s="73" t="str">
+        <v>93</v>
+      </c>
+      <c r="BM40" s="73">
         <f>IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="BN40" s="71" t="str">
         <f>IF(SUM(BN8:BN37)=0,"",MAX(BN8:BN37))</f>
@@ -7987,13 +8070,13 @@
         <f>IF(SUM(BO8:BO37)=0,"",MAX(BO8:BO37))</f>
         <v/>
       </c>
-      <c r="BP40" s="74" t="str">
+      <c r="BP40" s="74">
         <f>IF(SUM(BP8:BP37)=0,"",MAX(BP8:BP37))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="BQ40" s="62">
         <f>IF(SUM(BQ8:BQ37)=0,"",MAX(BQ8:BQ37))</f>
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="BR40" s="63" t="str">
         <f>IF(SUM(BR8:BR37)=0,"",MAX(BR8:BR37))</f>
@@ -8005,17 +8088,17 @@
       </c>
       <c r="BT40" s="65">
         <f>IF(SUM(BT8:BT37)=0,"",MAX(BT8:BT37))</f>
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" s="92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B41" s="93"/>
       <c r="C41" s="62">
         <f>IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D41" s="63" t="str">
         <f>IF(SUM(D8:D37)=0,"",MIN(D8:D37))</f>
@@ -8027,11 +8110,11 @@
       </c>
       <c r="F41" s="65">
         <f>IF(SUM(F8:F37)=0,"",MIN(F8:F37))</f>
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G41" s="62">
         <f>IF(SUM(G8:G37)=0,"",MIN(G8:G37))</f>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H41" s="63" t="str">
         <f>IF(SUM(H8:H37)=0,"",MIN(H8:H37))</f>
@@ -8043,11 +8126,11 @@
       </c>
       <c r="J41" s="65">
         <f>IF(SUM(J8:J37)=0,"",MIN(J8:J37))</f>
-        <v>13</v>
-      </c>
-      <c r="K41" s="62" t="str">
+        <v>22</v>
+      </c>
+      <c r="K41" s="62">
         <f>IF(SUM(K8:K37)=0,"",MIN(K8:K37))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="L41" s="63" t="str">
         <f>IF(SUM(L8:L37)=0,"",MIN(L8:L37))</f>
@@ -8057,13 +8140,13 @@
         <f>IF(SUM(M8:M37)=0,"",MIN(M8:M37))</f>
         <v/>
       </c>
-      <c r="N41" s="65" t="str">
+      <c r="N41" s="65">
         <f>IF(SUM(N8:N37)=0,"",MIN(N8:N37))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="O41" s="63">
         <f>IF(SUM(O8:O37)=0,"",MIN(O8:O37))</f>
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="P41" s="63" t="str">
         <f>IF(SUM(P8:P37)=0,"",MIN(P8:P37))</f>
@@ -8075,11 +8158,11 @@
       </c>
       <c r="R41" s="66">
         <f>IF(SUM(R8:R37)=0,"",MIN(R8:R37))</f>
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="S41" s="62">
         <f>IF(SUM(S8:S37)=0,"",MIN(S8:S37))</f>
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="T41" s="63" t="str">
         <f>IF(SUM(T8:T37)=0,"",MIN(T8:T37))</f>
@@ -8091,11 +8174,11 @@
       </c>
       <c r="V41" s="65">
         <f>IF(SUM(V8:V37)=0,"",MIN(V8:V37))</f>
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="W41" s="62">
         <f>IF(SUM(W8:W37)=0,"",MIN(W8:W37))</f>
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="X41" s="63" t="str">
         <f>IF(SUM(X8:X37)=0,"",MIN(X8:X37))</f>
@@ -8107,11 +8190,11 @@
       </c>
       <c r="Z41" s="65">
         <f>IF(SUM(Z8:Z37)=0,"",MIN(Z8:Z37))</f>
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AA41" s="63">
         <f>IF(SUM(AA8:AA37)=0,"",MIN(AA8:AA37))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AB41" s="63" t="str">
         <f>IF(SUM(AB8:AB37)=0,"",MIN(AB8:AB37))</f>
@@ -8123,7 +8206,7 @@
       </c>
       <c r="AD41" s="66">
         <f>IF(SUM(AD8:AD37)=0,"",MIN(AD8:AD37))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AE41" s="62" t="str">
         <f>IF(SUM(AE8:AE37)=0,"",MIN(AE8:AE37))</f>
@@ -8143,7 +8226,7 @@
       </c>
       <c r="AI41" s="62">
         <f>IF(SUM(AI8:AI37)=0,"",MIN(AI8:AI37))</f>
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AJ41" s="63" t="str">
         <f>IF(SUM(AJ8:AJ37)=0,"",MIN(AJ8:AJ37))</f>
@@ -8155,11 +8238,11 @@
       </c>
       <c r="AL41" s="65">
         <f>IF(SUM(AL8:AL37)=0,"",MIN(AL8:AL37))</f>
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AM41" s="62">
         <f>IF(SUM(AM8:AM37)=0,"",MIN(AM8:AM37))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN41" s="63" t="str">
         <f>IF(SUM(AN8:AN37)=0,"",MIN(AN8:AN37))</f>
@@ -8171,11 +8254,11 @@
       </c>
       <c r="AP41" s="65">
         <f>IF(SUM(AP8:AP37)=0,"",MIN(AP8:AP37))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ41" s="62">
         <f>IF(SUM(AQ8:AQ37)=0,"",MIN(AQ8:AQ37))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR41" s="63" t="str">
         <f>IF(SUM(AR8:AR37)=0,"",MIN(AR8:AR37))</f>
@@ -8187,11 +8270,11 @@
       </c>
       <c r="AT41" s="65">
         <f>IF(SUM(AT8:AT37)=0,"",MIN(AT8:AT37))</f>
-        <v>18</v>
-      </c>
-      <c r="AU41" s="62" t="str">
+        <v>16</v>
+      </c>
+      <c r="AU41" s="62">
         <f>IF(SUM(AU8:AU37)=0,"",MIN(AU8:AU37))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="AV41" s="63" t="str">
         <f>IF(SUM(AV8:AV37)=0,"",MIN(AV8:AV37))</f>
@@ -8201,13 +8284,13 @@
         <f>IF(SUM(AW8:AW37)=0,"",MIN(AW8:AW37))</f>
         <v/>
       </c>
-      <c r="AX41" s="65" t="str">
+      <c r="AX41" s="65">
         <f>IF(SUM(AX8:AX37)=0,"",MIN(AX8:AX37))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="AY41" s="63">
         <f>IF(SUM(AY8:AY37)=0,"",MIN(AY8:AY37))</f>
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AZ41" s="63" t="str">
         <f>IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
@@ -8219,11 +8302,11 @@
       </c>
       <c r="BB41" s="66">
         <f>IF(SUM(BB8:BB37)=0,"",MIN(BB8:BB37))</f>
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="BC41" s="67">
         <f>IF(SUM(BC8:BC37)=0,"",MIN(BC8:BC37))</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD41" s="68" t="str">
         <f>IF(SUM(BD8:BD37)=0,"",MIN(BD8:BD37))</f>
@@ -8235,15 +8318,15 @@
       </c>
       <c r="BF41" s="70">
         <f>IF(SUM(BF8:BF37)=0,"",MIN(BF8:BF37))</f>
-        <v>33.9</v>
+        <v>35.64</v>
       </c>
       <c r="BG41" s="92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BH41" s="93"/>
       <c r="BI41" s="73">
         <f>IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="BJ41" s="71" t="str">
         <f>IF(SUM(BJ8:BJ37)=0,"",MIN(BJ8:BJ37))</f>
@@ -8255,11 +8338,11 @@
       </c>
       <c r="BL41" s="74">
         <f>IF(SUM(BL8:BL37)=0,"",MIN(BL8:BL37))</f>
-        <v>25</v>
-      </c>
-      <c r="BM41" s="73" t="str">
+        <v>16</v>
+      </c>
+      <c r="BM41" s="73">
         <f>IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="BN41" s="71" t="str">
         <f>IF(SUM(BN8:BN37)=0,"",MIN(BN8:BN37))</f>
@@ -8269,13 +8352,13 @@
         <f>IF(SUM(BO8:BO37)=0,"",MIN(BO8:BO37))</f>
         <v/>
       </c>
-      <c r="BP41" s="74" t="str">
+      <c r="BP41" s="74">
         <f>IF(SUM(BP8:BP37)=0,"",MIN(BP8:BP37))</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="BQ41" s="62">
         <f>IF(SUM(BQ8:BQ37)=0,"",MIN(BQ8:BQ37))</f>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BR41" s="63" t="str">
         <f>IF(SUM(BR8:BR37)=0,"",MIN(BR8:BR37))</f>
@@ -8287,17 +8370,17 @@
       </c>
       <c r="BT41" s="65">
         <f>IF(SUM(BT8:BT37)=0,"",MIN(BT8:BT37))</f>
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" s="99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B42" s="100"/>
       <c r="C42" s="77">
         <f>IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D42" s="78" t="str">
         <f>IF(D38="","",COUNTIF(D8:D37,"&lt;51")/COUNT(D8:D37)*100)</f>
@@ -8309,11 +8392,11 @@
       </c>
       <c r="F42" s="80">
         <f>IF(F38="","",COUNTIF(F8:F37,"&lt;51")/COUNT(F8:F37)*100)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G42" s="77">
         <f>IF(G38="","",COUNTIF(G8:G37,"&lt;51")/COUNT(G8:G37)*100)</f>
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="H42" s="78" t="str">
         <f>IF(H38="","",COUNTIF(H8:H37,"&lt;51")/COUNT(H8:H37)*100)</f>
@@ -8325,11 +8408,11 @@
       </c>
       <c r="J42" s="80">
         <f>IF(J38="","",COUNTIF(J8:J37,"&lt;51")/COUNT(J8:J37)*100)</f>
-        <v>100</v>
-      </c>
-      <c r="K42" s="77" t="str">
+        <v>16</v>
+      </c>
+      <c r="K42" s="77">
         <f>IF(K38="","",COUNTIF(K8:K37,"&lt;51")/COUNT(K8:K37)*100)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="L42" s="78" t="str">
         <f>IF(L38="","",COUNTIF(L8:L37,"&lt;51")/COUNT(L8:L37)*100)</f>
@@ -8339,13 +8422,13 @@
         <f>IF(M38="","",COUNTIF(M8:M37,"&lt;51")/COUNT(M8:M37)*100)</f>
         <v/>
       </c>
-      <c r="N42" s="80" t="str">
+      <c r="N42" s="80">
         <f>IF(N38="","",COUNTIF(N8:N37,"&lt;51")/COUNT(N8:N37)*100)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="O42" s="78">
         <f>IF(O38="","",COUNTIF(O8:O37,"&lt;51")/COUNT(O8:O37)*100)</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="P42" s="78" t="str">
         <f>IF(P38="","",COUNTIF(P8:P37,"&lt;51")/COUNT(P8:P37)*100)</f>
@@ -8357,11 +8440,11 @@
       </c>
       <c r="R42" s="81">
         <f>IF(R38="","",COUNTIF(R8:R37,"&lt;51")/COUNT(R8:R37)*100)</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="S42" s="77">
         <f>IF(S38="","",COUNTIF(S8:S37,"&lt;51")/COUNT(S8:S37)*100)</f>
-        <v>29.166666666667</v>
+        <v>0</v>
       </c>
       <c r="T42" s="78" t="str">
         <f>IF(T38="","",COUNTIF(T8:T37,"&lt;51")/COUNT(T8:T37)*100)</f>
@@ -8373,11 +8456,11 @@
       </c>
       <c r="V42" s="80">
         <f>IF(V38="","",COUNTIF(V8:V37,"&lt;51")/COUNT(V8:V37)*100)</f>
-        <v>29.166666666667</v>
+        <v>0</v>
       </c>
       <c r="W42" s="77">
         <f>IF(W38="","",COUNTIF(W8:W37,"&lt;51")/COUNT(W8:W37)*100)</f>
-        <v>79.166666666667</v>
+        <v>12</v>
       </c>
       <c r="X42" s="78" t="str">
         <f>IF(X38="","",COUNTIF(X8:X37,"&lt;51")/COUNT(X8:X37)*100)</f>
@@ -8389,11 +8472,11 @@
       </c>
       <c r="Z42" s="80">
         <f>IF(Z38="","",COUNTIF(Z8:Z37,"&lt;51")/COUNT(Z8:Z37)*100)</f>
-        <v>79.166666666667</v>
+        <v>12</v>
       </c>
       <c r="AA42" s="78">
         <f>IF(AA38="","",COUNTIF(AA8:AA37,"&lt;51")/COUNT(AA8:AA37)*100)</f>
-        <v>29.166666666667</v>
+        <v>12</v>
       </c>
       <c r="AB42" s="78" t="str">
         <f>IF(AB38="","",COUNTIF(AB8:AB37,"&lt;51")/COUNT(AB8:AB37)*100)</f>
@@ -8405,7 +8488,7 @@
       </c>
       <c r="AD42" s="81">
         <f>IF(AD38="","",COUNTIF(AD8:AD37,"&lt;51")/COUNT(AD8:AD37)*100)</f>
-        <v>29.166666666667</v>
+        <v>12</v>
       </c>
       <c r="AE42" s="77" t="str">
         <f>IF(AE38="","",COUNTIF(AE8:AE37,"&lt;51")/COUNT(AE8:AE37)*100)</f>
@@ -8425,7 +8508,7 @@
       </c>
       <c r="AI42" s="77">
         <f>IF(AI38="","",COUNTIF(AI8:AI37,"&lt;51")/COUNT(AI8:AI37)*100)</f>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AJ42" s="78" t="str">
         <f>IF(AJ38="","",COUNTIF(AJ8:AJ37,"&lt;51")/COUNT(AJ8:AJ37)*100)</f>
@@ -8437,11 +8520,11 @@
       </c>
       <c r="AL42" s="80">
         <f>IF(AL38="","",COUNTIF(AL8:AL37,"&lt;51")/COUNT(AL8:AL37)*100)</f>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AM42" s="77">
         <f>IF(AM38="","",COUNTIF(AM8:AM37,"&lt;51")/COUNT(AM8:AM37)*100)</f>
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AN42" s="78" t="str">
         <f>IF(AN38="","",COUNTIF(AN8:AN37,"&lt;51")/COUNT(AN8:AN37)*100)</f>
@@ -8453,11 +8536,11 @@
       </c>
       <c r="AP42" s="80">
         <f>IF(AP38="","",COUNTIF(AP8:AP37,"&lt;51")/COUNT(AP8:AP37)*100)</f>
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AQ42" s="77">
         <f>IF(AQ38="","",COUNTIF(AQ8:AQ37,"&lt;51")/COUNT(AQ8:AQ37)*100)</f>
-        <v>37.5</v>
+        <v>8</v>
       </c>
       <c r="AR42" s="78" t="str">
         <f>IF(AR38="","",COUNTIF(AR8:AR37,"&lt;51")/COUNT(AR8:AR37)*100)</f>
@@ -8469,11 +8552,11 @@
       </c>
       <c r="AT42" s="80">
         <f>IF(AT38="","",COUNTIF(AT8:AT37,"&lt;51")/COUNT(AT8:AT37)*100)</f>
-        <v>37.5</v>
-      </c>
-      <c r="AU42" s="77" t="str">
+        <v>8</v>
+      </c>
+      <c r="AU42" s="77">
         <f>IF(AU38="","",COUNTIF(AU8:AU37,"&lt;51")/COUNT(AU8:AU37)*100)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AV42" s="78" t="str">
         <f>IF(AV38="","",COUNTIF(AV8:AV37,"&lt;51")/COUNT(AV8:AV37)*100)</f>
@@ -8483,13 +8566,13 @@
         <f>IF(AW38="","",COUNTIF(AW8:AW37,"&lt;51")/COUNT(AW8:AW37)*100)</f>
         <v/>
       </c>
-      <c r="AX42" s="80" t="str">
+      <c r="AX42" s="80">
         <f>IF(AX38="","",COUNTIF(AX8:AX37,"&lt;51")/COUNT(AX8:AX37)*100)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AY42" s="78">
         <f>IF(AY38="","",COUNTIF(AY8:AY37,"&lt;51")/COUNT(AY8:AY37)*100)</f>
-        <v>29.166666666667</v>
+        <v>0</v>
       </c>
       <c r="AZ42" s="78" t="str">
         <f>IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
@@ -8501,11 +8584,11 @@
       </c>
       <c r="BB42" s="81">
         <f>IF(BB38="","",COUNTIF(BB8:BB37,"&lt;51")/COUNT(BB8:BB37)*100)</f>
-        <v>29.166666666667</v>
+        <v>0</v>
       </c>
       <c r="BC42" s="82">
         <f>IF(BC38="","",COUNTIF(BC8:BC37,"&lt;51")/COUNT(BC8:BC37)*100)</f>
-        <v>70.833333333333</v>
+        <v>12</v>
       </c>
       <c r="BD42" s="83" t="str">
         <f>IF(BD38="","",COUNTIF(BD8:BD37,"&lt;51")/COUNT(BD8:BD37)*100)</f>
@@ -8517,15 +8600,15 @@
       </c>
       <c r="BF42" s="85">
         <f>IF(BF38="","",COUNTIF(BF8:BF37,"&lt;51")/COUNT(BF8:BF37)*100)</f>
-        <v>37.5</v>
+        <v>8</v>
       </c>
       <c r="BG42" s="134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BH42" s="135"/>
       <c r="BI42" s="88">
         <f>IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
-        <v>20.833333333333</v>
+        <v>12</v>
       </c>
       <c r="BJ42" s="86" t="str">
         <f>IF(BJ38="","",COUNTIF(BJ8:BJ37,"&lt;51")/COUNT(BJ8:BJ37)*100)</f>
@@ -8537,11 +8620,11 @@
       </c>
       <c r="BL42" s="89">
         <f>IF(BL38="","",COUNTIF(BL8:BL37,"&lt;51")/COUNT(BL8:BL37)*100)</f>
-        <v>20.833333333333</v>
-      </c>
-      <c r="BM42" s="88" t="str">
+        <v>12</v>
+      </c>
+      <c r="BM42" s="88">
         <f>IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="BN42" s="86" t="str">
         <f>IF(BN38="","",COUNTIF(BN8:BN37,"&lt;51")/COUNT(BN8:BN37)*100)</f>
@@ -8551,13 +8634,13 @@
         <f>IF(BO38="","",COUNTIF(BO8:BO37,"&lt;51")/COUNT(BO8:BO37)*100)</f>
         <v/>
       </c>
-      <c r="BP42" s="89" t="str">
+      <c r="BP42" s="89">
         <f>IF(BP38="","",COUNTIF(BP8:BP37,"&lt;51")/COUNT(BP8:BP37)*100)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="BQ42" s="77">
         <f>IF(BQ38="","",COUNTIF(BQ8:BQ37,"&lt;51")/COUNT(BQ8:BQ37)*100)</f>
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="BR42" s="78" t="str">
         <f>IF(BR38="","",COUNTIF(BR8:BR37,"&lt;51")/COUNT(BR8:BR37)*100)</f>
@@ -8569,12 +8652,12 @@
       </c>
       <c r="BT42" s="80">
         <f>IF(BT38="","",COUNTIF(BT8:BT37,"&lt;51")/COUNT(BT8:BT37)*100)</f>
-        <v>100</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:80" customHeight="1" ht="12.75"/>
@@ -8586,7 +8669,7 @@
     <row r="50" spans="1:80" customHeight="1" ht="12.75"/>
     <row r="51" spans="1:80">
       <c r="B51" s="126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C51" s="126"/>
       <c r="D51" s="126"/>
@@ -8603,7 +8686,7 @@
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R51" s="126"/>
       <c r="S51" s="126"/>
@@ -8622,7 +8705,7 @@
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
       <c r="AH51" s="126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AI51" s="126"/>
       <c r="AJ51" s="126"/>
@@ -8642,14 +8725,14 @@
       <c r="AX51" s="1"/>
       <c r="AY51" s="1"/>
       <c r="BG51" s="126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BH51" s="126"/>
       <c r="BI51" s="90"/>
       <c r="BJ51" s="76"/>
       <c r="BK51" s="76"/>
       <c r="BL51" s="126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BM51" s="126"/>
       <c r="BN51" s="126"/>
@@ -8667,7 +8750,7 @@
     </row>
     <row r="52" spans="1:80">
       <c r="B52" s="127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" s="127"/>
       <c r="D52" s="127"/>
@@ -8684,7 +8767,7 @@
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="127" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R52" s="127"/>
       <c r="S52" s="127"/>
@@ -8703,7 +8786,7 @@
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
       <c r="AH52" s="127" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI52" s="127"/>
       <c r="AJ52" s="127"/>
@@ -8723,17 +8806,17 @@
       <c r="AX52" s="1"/>
       <c r="AY52" s="1"/>
       <c r="BE52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BG52" s="127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BH52" s="127"/>
       <c r="BI52" s="91"/>
       <c r="BJ52" s="76"/>
       <c r="BK52" s="76"/>
       <c r="BL52" s="127" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BM52" s="127"/>
       <c r="BN52" s="127"/>
@@ -8748,7 +8831,7 @@
       <c r="BW52" s="76"/>
       <c r="BX52" s="76"/>
       <c r="BY52" s="75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
